--- a/Stock_Analysis_Output.xlsx
+++ b/Stock_Analysis_Output.xlsx
@@ -794,29 +794,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AMOC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EGX30</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>AMOC</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>EGX30</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>13.6</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2822</v>
+        <v>0.2656</v>
       </c>
       <c r="G2" t="n">
         <v>0.0611</v>
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>18.0017</v>
+        <v>17.2021</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -841,25 +841,25 @@
         <v>7.83</v>
       </c>
       <c r="M2" t="n">
-        <v>1.8384</v>
+        <v>1.7374</v>
       </c>
       <c r="N2" t="n">
-        <v>8765570</v>
+        <v>8835435</v>
       </c>
       <c r="O2" t="n">
         <v>19695350</v>
       </c>
       <c r="P2" t="n">
-        <v>2.247</v>
+        <v>2.229</v>
       </c>
       <c r="Q2" t="n">
-        <v>6719781</v>
+        <v>6703469</v>
       </c>
       <c r="R2" t="n">
-        <v>9700237</v>
+        <v>2372943</v>
       </c>
       <c r="S2" t="n">
-        <v>1.444</v>
+        <v>0.354</v>
       </c>
       <c r="T2" t="n">
         <v>10.65</v>
@@ -938,17 +938,17 @@
         </is>
       </c>
       <c r="AP2" t="n">
-        <v>-846598128</v>
+        <v>-861547592</v>
       </c>
       <c r="AQ2" t="n">
-        <v>52083001</v>
+        <v>38586692</v>
       </c>
       <c r="AR2" t="n">
-        <v>58.4</v>
+        <v>58.09</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:17</t>
+          <t>2026-09-11 18:20:09</t>
         </is>
       </c>
       <c r="AT2" t="n">
@@ -1001,11 +1001,11 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 55.2% above EMA200, MACD bullish (strength 11%), MACD above zero (confirmed momentum), RSI mildly overbought (71.2) (strong trend maintained), volume 2.25x average, accumulation (ADL rising over last 20d); score=54.1/100; entry: enhanced entry at VWMA (overbought (RSI: 71.2)), +0.35% buffer</t>
+          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 55.2% above EMA200, MACD bullish (strength 11%), MACD above zero (confirmed momentum), RSI mildly overbought (71.2) (strong trend maintained), volume 2.23x average, accumulation (ADL rising over last 20d); score=52.6/100; entry: enhanced entry at VWMA (overbought (RSI: 71.2)), +0.35% buffer</t>
         </is>
       </c>
       <c r="BI2" t="n">
-        <v>54.14</v>
+        <v>52.55</v>
       </c>
       <c r="BJ2" t="n">
         <v>10.09</v>
@@ -1017,7 +1017,7 @@
         <v>13.79</v>
       </c>
       <c r="BM2" t="n">
-        <v>13.97</v>
+        <v>12.38</v>
       </c>
       <c r="BN2" t="n">
         <v>10.38</v>
@@ -1027,19 +1027,19 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>0.3515</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT2" t="n">
         <v>0</v>
@@ -1048,29 +1048,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ARCC</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EGX30</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ARCC</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>EGX30</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>76.45</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4905</v>
+        <v>1.4928</v>
       </c>
       <c r="G3" t="n">
         <v>0.09470000000000001</v>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>580.0857999999999</v>
+        <v>583.2904</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -1095,31 +1095,31 @@
         <v>0.91</v>
       </c>
       <c r="M3" t="n">
-        <v>83.7448</v>
+        <v>84.2406</v>
       </c>
       <c r="N3" t="n">
-        <v>793269</v>
+        <v>793615</v>
       </c>
       <c r="O3" t="n">
         <v>188473</v>
       </c>
       <c r="P3" t="n">
-        <v>0.238</v>
+        <v>0.237</v>
       </c>
       <c r="Q3" t="n">
-        <v>407630</v>
+        <v>411278</v>
       </c>
       <c r="R3" t="n">
-        <v>37867</v>
+        <v>182629</v>
       </c>
       <c r="S3" t="n">
-        <v>0.093</v>
+        <v>0.444</v>
       </c>
       <c r="T3" t="n">
         <v>71.51000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>91.72</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>65.1268</v>
@@ -1194,17 +1194,17 @@
         </is>
       </c>
       <c r="AP3" t="n">
-        <v>22845652206871</v>
+        <v>22845653274216</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-7547321</v>
+        <v>-2808339</v>
       </c>
       <c r="AR3" t="n">
-        <v>66.47</v>
+        <v>66.45</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:17</t>
+          <t>2026-09-11 18:20:09</t>
         </is>
       </c>
       <c r="AT3" t="n">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="BR3" t="n">
-        <v>0.3941</v>
+        <v>0.3587</v>
       </c>
       <c r="BS3" t="n">
         <v>1</v>
@@ -1304,29 +1304,29 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>EFID</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EGX30</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>EFID</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>EGX30</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>31.2</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6276</v>
+        <v>0.6092</v>
       </c>
       <c r="G4" t="n">
         <v>0.2476</v>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>22.6706</v>
+        <v>22.1999</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1351,25 +1351,25 @@
         <v>12.86</v>
       </c>
       <c r="M4" t="n">
-        <v>2.4893</v>
+        <v>2.427</v>
       </c>
       <c r="N4" t="n">
-        <v>1636737</v>
+        <v>1643695</v>
       </c>
       <c r="O4" t="n">
         <v>1935019</v>
       </c>
       <c r="P4" t="n">
-        <v>1.182</v>
+        <v>1.177</v>
       </c>
       <c r="Q4" t="n">
-        <v>1172578</v>
+        <v>1167575</v>
       </c>
       <c r="R4" t="n">
-        <v>2185811</v>
+        <v>272113</v>
       </c>
       <c r="S4" t="n">
-        <v>1.864</v>
+        <v>0.233</v>
       </c>
       <c r="T4" t="n">
         <v>31.1</v>
@@ -1450,17 +1450,17 @@
         </is>
       </c>
       <c r="AP4" t="n">
-        <v>191059108908622</v>
+        <v>191059131617015</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-842270</v>
+        <v>-3623220</v>
       </c>
       <c r="AR4" t="n">
-        <v>63.24</v>
+        <v>63.1</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:17</t>
+          <t>2026-09-11 18:20:09</t>
         </is>
       </c>
       <c r="AT4" t="n">
@@ -1513,11 +1513,11 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 14.3% above EMA200, MACD below signal (bearish), RSI in healthy bullish zone (51.1), buy-volume spike (1.86x), distribution (ADL falling over last 20d), support bounce confirmed by volume; score=62.0/100; entry: enhanced entry at Swing Support (overbought (RSI: 51.1)), +0.35% buffer</t>
+          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 14.3% above EMA200, MACD below signal (bearish), RSI in healthy bullish zone (51.1), distribution (ADL falling over last 20d), price near support; score=52.6/100; entry: enhanced entry at Swing Support (overbought (RSI: 51.1)), +0.35% buffer</t>
         </is>
       </c>
       <c r="BI4" t="n">
-        <v>62.01</v>
+        <v>52.59</v>
       </c>
       <c r="BJ4" t="n">
         <v>9.01</v>
@@ -1529,29 +1529,29 @@
         <v>27.58</v>
       </c>
       <c r="BM4" t="n">
-        <v>8.720000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BN4" t="n">
         <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>16.7</v>
+        <v>15.43</v>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="BR4" t="n">
-        <v>0.3014</v>
+        <v>0.4815</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT4" t="n">
         <v>1</v>
@@ -1560,29 +1560,29 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>EFIH</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EGX30</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>EFIH</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>EGX30</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>23.99</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4703</v>
+        <v>0.4684</v>
       </c>
       <c r="G5" t="n">
         <v>0.2148</v>
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>8.0097</v>
+        <v>8.0123</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1607,10 +1607,10 @@
         <v>31.84</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7532</v>
+        <v>0.7536</v>
       </c>
       <c r="N5" t="n">
-        <v>3421009</v>
+        <v>3418227</v>
       </c>
       <c r="O5" t="n">
         <v>1392391</v>
@@ -1619,19 +1619,19 @@
         <v>0.407</v>
       </c>
       <c r="Q5" t="n">
-        <v>1766324</v>
+        <v>1783635</v>
       </c>
       <c r="R5" t="n">
-        <v>2084650</v>
+        <v>1392391</v>
       </c>
       <c r="S5" t="n">
-        <v>1.18</v>
+        <v>0.781</v>
       </c>
       <c r="T5" t="n">
         <v>23.27</v>
       </c>
       <c r="U5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="V5" t="n">
         <v>23.2466</v>
@@ -1706,17 +1706,17 @@
         </is>
       </c>
       <c r="AP5" t="n">
-        <v>17212778</v>
+        <v>18605169</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-60167</v>
+        <v>6435312</v>
       </c>
       <c r="AR5" t="n">
-        <v>58.14</v>
+        <v>58.17</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:17</t>
+          <t>2026-09-11 18:20:09</t>
         </is>
       </c>
       <c r="AT5" t="n">
@@ -1764,16 +1764,16 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 16.8% above EMA200, MACD below signal (bearish), RSI in healthy bullish zone (54.2), distribution (ADL falling over last 20d); score=37.4/100; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 54.2)), +0.35% buffer</t>
+          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 16.8% above EMA200, MACD below signal (bearish), RSI in healthy bullish zone (54.2), accumulation (ADL rising over last 20d); score=47.2/100; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 54.2)), +0.35% buffer</t>
         </is>
       </c>
       <c r="BI5" t="n">
-        <v>37.43</v>
+        <v>47.22</v>
       </c>
       <c r="BJ5" t="n">
         <v>9.26</v>
@@ -1785,10 +1785,10 @@
         <v>27.58</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.59</v>
+        <v>0</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>10.38</v>
       </c>
       <c r="BO5" t="n">
         <v>0</v>
@@ -1804,41 +1804,41 @@
         </is>
       </c>
       <c r="BR5" t="n">
-        <v>0.3689</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>EGAL</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EGX30</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>EGAL</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>EGX30</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>377.99</v>
       </c>
       <c r="F6" t="n">
-        <v>7.2666</v>
+        <v>7.3808</v>
       </c>
       <c r="G6" t="n">
         <v>0.1054</v>
@@ -1852,7 +1852,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>753.9363</v>
+        <v>766.9345</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1863,10 +1863,10 @@
         <v>3.96</v>
       </c>
       <c r="M6" t="n">
-        <v>93.66370000000001</v>
+        <v>95.5154</v>
       </c>
       <c r="N6" t="n">
-        <v>337544</v>
+        <v>337664</v>
       </c>
       <c r="O6" t="n">
         <v>137677</v>
@@ -1875,18 +1875,20 @@
         <v>0.408</v>
       </c>
       <c r="Q6" t="n">
-        <v>137476</v>
+        <v>140656</v>
       </c>
       <c r="R6" t="n">
-        <v>10249</v>
+        <v>137677</v>
       </c>
       <c r="S6" t="n">
-        <v>0.075</v>
+        <v>0.979</v>
       </c>
       <c r="T6" t="n">
         <v>321.01</v>
       </c>
-      <c r="U6" t="inlineStr"/>
+      <c r="U6" t="n">
+        <v>395</v>
+      </c>
       <c r="V6" t="n">
         <v>322.6402</v>
       </c>
@@ -1960,17 +1962,17 @@
         </is>
       </c>
       <c r="AP6" t="n">
-        <v>5694283975451</v>
+        <v>5694284010333</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-1244610</v>
+        <v>-489699</v>
       </c>
       <c r="AR6" t="n">
-        <v>63.66</v>
+        <v>63.72</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:17</t>
+          <t>2026-09-11 18:20:09</t>
         </is>
       </c>
       <c r="AT6" t="n">
@@ -2058,10 +2060,10 @@
         </is>
       </c>
       <c r="BR6" t="n">
-        <v>0.5407</v>
+        <v>0.3705</v>
       </c>
       <c r="BS6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT6" t="n">
         <v>0</v>
@@ -2070,29 +2072,29 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ISPH</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EGX30</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ISPH</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>EGX30</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>12.98</v>
       </c>
       <c r="F7" t="n">
-        <v>0.254</v>
+        <v>0.2535</v>
       </c>
       <c r="G7" t="n">
         <v>0.039</v>
@@ -2106,7 +2108,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>30.2479</v>
+        <v>30.3086</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -2117,25 +2119,25 @@
         <v>3.5</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7</v>
+        <v>3.7086</v>
       </c>
       <c r="N7" t="n">
-        <v>6741886</v>
+        <v>6716602</v>
       </c>
       <c r="O7" t="n">
         <v>2624627</v>
       </c>
       <c r="P7" t="n">
-        <v>0.389</v>
+        <v>0.391</v>
       </c>
       <c r="Q7" t="n">
-        <v>3521760</v>
+        <v>3520160</v>
       </c>
       <c r="R7" t="n">
-        <v>654808</v>
+        <v>1312306</v>
       </c>
       <c r="S7" t="n">
-        <v>0.186</v>
+        <v>0.373</v>
       </c>
       <c r="T7" t="n">
         <v>12.75</v>
@@ -2216,17 +2218,17 @@
         </is>
       </c>
       <c r="AP7" t="n">
-        <v>1905064156279</v>
+        <v>1905064156263</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-54033147</v>
+        <v>-46309623</v>
       </c>
       <c r="AR7" t="n">
-        <v>62.46</v>
+        <v>62.43</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:17</t>
+          <t>2026-09-11 18:20:09</t>
         </is>
       </c>
       <c r="AT7" t="n">
@@ -2305,50 +2307,50 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid</t>
         </is>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>0.3028</v>
       </c>
       <c r="BS7" t="n">
         <v>0</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>JUFO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EGX30</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>JUFO</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>EGX30</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>27.35</v>
       </c>
       <c r="F8" t="n">
-        <v>0.536</v>
+        <v>0.534</v>
       </c>
       <c r="G8" t="n">
         <v>0.2392</v>
@@ -2362,7 +2364,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>21.8202</v>
+        <v>21.8331</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -2373,25 +2375,25 @@
         <v>12.39</v>
       </c>
       <c r="M8" t="n">
-        <v>2.2057</v>
+        <v>2.2073</v>
       </c>
       <c r="N8" t="n">
-        <v>1332977</v>
+        <v>1327524</v>
       </c>
       <c r="O8" t="n">
         <v>355658</v>
       </c>
       <c r="P8" t="n">
-        <v>0.267</v>
+        <v>0.268</v>
       </c>
       <c r="Q8" t="n">
-        <v>696135</v>
+        <v>703202</v>
       </c>
       <c r="R8" t="n">
-        <v>235067</v>
+        <v>355658</v>
       </c>
       <c r="S8" t="n">
-        <v>0.338</v>
+        <v>0.506</v>
       </c>
       <c r="T8" t="n">
         <v>26.45</v>
@@ -2472,17 +2474,17 @@
         </is>
       </c>
       <c r="AP8" t="n">
-        <v>23880742143958</v>
+        <v>23880740703852</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-312054</v>
+        <v>-1774614</v>
       </c>
       <c r="AR8" t="n">
-        <v>58.95</v>
+        <v>59</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:17</t>
+          <t>2026-09-11 18:20:09</t>
         </is>
       </c>
       <c r="AT8" t="n">
@@ -2570,41 +2572,41 @@
         </is>
       </c>
       <c r="BR8" t="n">
-        <v>0.4386</v>
+        <v>0.488</v>
       </c>
       <c r="BS8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BT8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MCQE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EGX30</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>MCQE</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>EGX30</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>235</v>
       </c>
       <c r="F9" t="n">
-        <v>4.718</v>
+        <v>4.5887</v>
       </c>
       <c r="G9" t="n">
         <v>0.1455</v>
@@ -2618,7 +2620,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>2341.2633</v>
+        <v>2290.9481</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -2629,31 +2631,31 @@
         <v>0.7</v>
       </c>
       <c r="M9" t="n">
-        <v>345.3652</v>
+        <v>337.4934</v>
       </c>
       <c r="N9" t="n">
-        <v>168193</v>
+        <v>167772</v>
       </c>
       <c r="O9" t="n">
         <v>62754</v>
       </c>
       <c r="P9" t="n">
-        <v>0.373</v>
+        <v>0.374</v>
       </c>
       <c r="Q9" t="n">
-        <v>77343</v>
+        <v>76950</v>
       </c>
       <c r="R9" t="n">
-        <v>27025</v>
+        <v>5229</v>
       </c>
       <c r="S9" t="n">
-        <v>0.349</v>
+        <v>0.068</v>
       </c>
       <c r="T9" t="n">
         <v>178</v>
       </c>
       <c r="U9" t="n">
-        <v>292.32</v>
+        <v>254.23</v>
       </c>
       <c r="V9" t="n">
         <v>207.5862</v>
@@ -2728,17 +2730,17 @@
         </is>
       </c>
       <c r="AP9" t="n">
-        <v>17855038391561</v>
+        <v>17855038528542</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-1313352</v>
+        <v>-1155496</v>
       </c>
       <c r="AR9" t="n">
-        <v>68.66</v>
+        <v>68.61</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:17</t>
+          <t>2026-09-11 18:20:09</t>
         </is>
       </c>
       <c r="AT9" t="n">
@@ -2838,29 +2840,29 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ORAS</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EGX30</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ORAS</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>EGX30</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>858</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3934</v>
+        <v>1.3873</v>
       </c>
       <c r="G10" t="n">
         <v>1.3</v>
@@ -2976,7 +2978,7 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:17</t>
+          <t>2026-09-11 18:20:09</t>
         </is>
       </c>
       <c r="AT10" t="n">
@@ -3076,29 +3078,29 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ORWE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EGX30</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>ORWE</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>EGX30</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>28.19</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5474</v>
+        <v>0.5504</v>
       </c>
       <c r="G11" t="n">
         <v>0.1517</v>
@@ -3112,7 +3114,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>44.0135</v>
+        <v>44.3351</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -3123,25 +3125,25 @@
         <v>8.31</v>
       </c>
       <c r="M11" t="n">
-        <v>3.359</v>
+        <v>3.3927</v>
       </c>
       <c r="N11" t="n">
-        <v>1438086</v>
+        <v>1440185</v>
       </c>
       <c r="O11" t="n">
         <v>989198</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>1335961</v>
+        <v>1358213</v>
       </c>
       <c r="R11" t="n">
-        <v>736213</v>
+        <v>989198</v>
       </c>
       <c r="S11" t="n">
-        <v>0.551</v>
+        <v>0.728</v>
       </c>
       <c r="T11" t="n">
         <v>24.5</v>
@@ -3220,17 +3222,17 @@
         </is>
       </c>
       <c r="AP11" t="n">
-        <v>-99698348</v>
+        <v>-98709150</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-918451</v>
+        <v>4558488</v>
       </c>
       <c r="AR11" t="n">
-        <v>59.54</v>
+        <v>59.53</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:17</t>
+          <t>2026-09-11 18:20:09</t>
         </is>
       </c>
       <c r="AT11" t="n">
@@ -3278,16 +3280,16 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 18.6% above EMA200, MACD bullish (strength 13%), MACD above zero (confirmed momentum), RSI in healthy bullish zone (63.3), distribution (ADL falling over last 20d); score=43.0/100; entry: enhanced entry at VWMA (overbought (RSI: 63.3)), +0.35% buffer</t>
+          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 18.6% above EMA200, MACD bullish (strength 13%), MACD above zero (confirmed momentum), RSI in healthy bullish zone (63.3), accumulation (ADL rising over last 20d); score=53.4/100; entry: enhanced entry at VWMA (overbought (RSI: 63.3)), +0.35% buffer</t>
         </is>
       </c>
       <c r="BI11" t="n">
-        <v>43.05</v>
+        <v>53.42</v>
       </c>
       <c r="BJ11" t="n">
         <v>9.44</v>
@@ -3302,26 +3304,26 @@
         <v>0</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>10.38</v>
       </c>
       <c r="BO11" t="n">
         <v>0</v>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid</t>
         </is>
       </c>
       <c r="BR11" t="n">
-        <v>0.3933</v>
+        <v>0.3458</v>
       </c>
       <c r="BS11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT11" t="n">
         <v>1</v>
@@ -3330,29 +3332,29 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PHDC</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EGX30</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>PHDC</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>EGX30</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>14.45</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2859</v>
+        <v>0.2822</v>
       </c>
       <c r="G12" t="n">
         <v>0.0482</v>
@@ -3366,7 +3368,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>38.94</v>
+        <v>38.6498</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -3377,28 +3379,28 @@
         <v>3.35</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3555</v>
+        <v>4.3166</v>
       </c>
       <c r="N12" t="n">
-        <v>17322926</v>
+        <v>17299456</v>
       </c>
       <c r="O12" t="n">
         <v>7541615</v>
       </c>
       <c r="P12" t="n">
-        <v>0.435</v>
+        <v>0.436</v>
       </c>
       <c r="Q12" t="n">
-        <v>5981424</v>
+        <v>5848081</v>
       </c>
       <c r="R12" t="n">
-        <v>5541904</v>
+        <v>1450315</v>
       </c>
       <c r="S12" t="n">
-        <v>0.927</v>
+        <v>0.248</v>
       </c>
       <c r="T12" t="n">
-        <v>14.32</v>
+        <v>14.4</v>
       </c>
       <c r="U12" t="n">
         <v>15.73</v>
@@ -3476,28 +3478,28 @@
         </is>
       </c>
       <c r="AP12" t="n">
-        <v>-1196673570</v>
+        <v>-1201314555</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-64775829</v>
+        <v>-53567385</v>
       </c>
       <c r="AR12" t="n">
-        <v>62.34</v>
+        <v>62.29</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:17</t>
+          <t>2026-09-11 18:20:09</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>14.3699</v>
+        <v>14.4502</v>
       </c>
       <c r="AU12" t="n">
-        <v>14.32</v>
+        <v>14.4424</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>stop at Swing Support</t>
+          <t>stop at Fibonacci S1</t>
         </is>
       </c>
       <c r="AW12" t="n">
@@ -3515,22 +3517,22 @@
         </is>
       </c>
       <c r="BA12" t="n">
-        <v>24.61</v>
+        <v>147.15</v>
       </c>
       <c r="BB12" t="n">
-        <v>29</v>
+        <v>175.18</v>
       </c>
       <c r="BC12" t="n">
-        <v>29.84</v>
+        <v>180.61</v>
       </c>
       <c r="BD12" t="n">
-        <v>8.550000000000001</v>
+        <v>7.95</v>
       </c>
       <c r="BE12" t="n">
-        <v>10.07</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="BF12" t="n">
-        <v>10.37</v>
+        <v>9.76</v>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
@@ -3539,11 +3541,11 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>EMA50 &gt; EMA200, price above EMA200, Diamond Cross (EMA20&gt;EMA50), price 19.0% above EMA200, MACD below signal (bearish), RSI neutral-firm (41.0), distribution (ADL falling over last 20d), price near support; score=37.1/100; entry: enhanced entry at Swing Support (neutral (RSI: 41.0)), +0.35% buffer</t>
+          <t>EMA50 &gt; EMA200, price above EMA200, Diamond Cross (EMA20&gt;EMA50), price 19.0% above EMA200, MACD below signal (bearish), RSI neutral-firm (41.0), distribution (ADL falling over last 20d), price near support; score=39.3/100; entry: enhanced entry at Swing Support (neutral (RSI: 41.0)), +0.35% buffer</t>
         </is>
       </c>
       <c r="BI12" t="n">
-        <v>37.12</v>
+        <v>39.34</v>
       </c>
       <c r="BJ12" t="n">
         <v>7.47</v>
@@ -3561,7 +3563,7 @@
         <v>0</v>
       </c>
       <c r="BO12" t="n">
-        <v>13.1</v>
+        <v>15.33</v>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
@@ -3586,29 +3588,29 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ETEL</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EGX30</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>ETEL</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>EGX30</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E13" t="n">
         <v>125.25</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4709</v>
+        <v>2.4457</v>
       </c>
       <c r="G13" t="n">
         <v>0.3545</v>
@@ -3622,7 +3624,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>454.3072</v>
+        <v>451.9814</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -3633,25 +3635,25 @@
         <v>2.24</v>
       </c>
       <c r="M13" t="n">
-        <v>56.2476</v>
+        <v>55.9172</v>
       </c>
       <c r="N13" t="n">
-        <v>1110094</v>
+        <v>1122994</v>
       </c>
       <c r="O13" t="n">
         <v>3747741</v>
       </c>
       <c r="P13" t="n">
-        <v>3.376</v>
+        <v>3.337</v>
       </c>
       <c r="Q13" t="n">
-        <v>545706</v>
+        <v>541204</v>
       </c>
       <c r="R13" t="n">
-        <v>3682138</v>
+        <v>132051</v>
       </c>
       <c r="S13" t="n">
-        <v>6.747</v>
+        <v>0.244</v>
       </c>
       <c r="T13" t="n">
         <v>112.5</v>
@@ -3730,17 +3732,17 @@
         </is>
       </c>
       <c r="AP13" t="n">
-        <v>-23715866</v>
+        <v>-27199505</v>
       </c>
       <c r="AQ13" t="n">
-        <v>2868838</v>
+        <v>-346418</v>
       </c>
       <c r="AR13" t="n">
-        <v>60.82</v>
+        <v>61.1</v>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:17</t>
+          <t>2026-09-11 18:20:09</t>
         </is>
       </c>
       <c r="AT13" t="n">
@@ -3761,11 +3763,11 @@
         <v>146</v>
       </c>
       <c r="AY13" t="n">
-        <v>135.8213</v>
+        <v>136.9444</v>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 129.6; TP2: Classic R3 at 146; TP3: ATR target (full) at 135.82</t>
+          <t>TP1: Classic R2 at 129.6; TP2: Classic R3 at 146; TP3: ATR target (full) at 136.94</t>
         </is>
       </c>
       <c r="BA13" t="n">
@@ -3775,7 +3777,7 @@
         <v>6.83</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.22</v>
+        <v>4.5</v>
       </c>
       <c r="BD13" t="n">
         <v>8.529999999999999</v>
@@ -3784,20 +3786,20 @@
         <v>22.26</v>
       </c>
       <c r="BF13" t="n">
-        <v>13.74</v>
+        <v>14.68</v>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 39.4% above EMA200, MACD bullish (strength 13%), MACD above zero (confirmed momentum), RSI mildly overbought (70.7) (strong trend maintained), volume 3.38x average, buy-volume spike (6.75x), accumulation (ADL rising over last 20d); score=56.5/100; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 70.7)), +0.35% buffer</t>
+          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 39.4% above EMA200, MACD bullish (strength 13%), MACD above zero (confirmed momentum), RSI mildly overbought (70.7) (strong trend maintained), volume 3.34x average, distribution (ADL falling over last 20d); score=47.8/100; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 70.7)), +0.35% buffer</t>
         </is>
       </c>
       <c r="BI13" t="n">
-        <v>56.45</v>
+        <v>47.8</v>
       </c>
       <c r="BJ13" t="n">
         <v>10.09</v>
@@ -3812,7 +3814,7 @@
         <v>17.9</v>
       </c>
       <c r="BN13" t="n">
-        <v>8.65</v>
+        <v>0</v>
       </c>
       <c r="BO13" t="n">
         <v>0</v>
@@ -3828,41 +3830,41 @@
         </is>
       </c>
       <c r="BR13" t="n">
-        <v>0.4809</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>RMDA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EGX30</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>RMDA</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>EGX30</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E14" t="n">
         <v>6.28</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1236</v>
+        <v>0.1226</v>
       </c>
       <c r="G14" t="n">
         <v>0.0401</v>
@@ -3876,7 +3878,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>4.1077</v>
+        <v>4.0972</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -3887,10 +3889,10 @@
         <v>15.27</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4127</v>
+        <v>0.4114</v>
       </c>
       <c r="N14" t="n">
-        <v>13377010</v>
+        <v>13360315</v>
       </c>
       <c r="O14" t="n">
         <v>2965157</v>
@@ -3899,13 +3901,13 @@
         <v>0.222</v>
       </c>
       <c r="Q14" t="n">
-        <v>6612145</v>
+        <v>6619803</v>
       </c>
       <c r="R14" t="n">
-        <v>1500209</v>
+        <v>1186067</v>
       </c>
       <c r="S14" t="n">
-        <v>0.227</v>
+        <v>0.179</v>
       </c>
       <c r="T14" t="n">
         <v>6</v>
@@ -3986,17 +3988,17 @@
         </is>
       </c>
       <c r="AP14" t="n">
-        <v>-2393183196133</v>
+        <v>-2393183789156</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-28164781</v>
+        <v>-18845384</v>
       </c>
       <c r="AR14" t="n">
-        <v>66.68000000000001</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:17</t>
+          <t>2026-09-11 18:20:09</t>
         </is>
       </c>
       <c r="AT14" t="n">
@@ -4096,29 +4098,29 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>AMER</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EGX70</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>AMER</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>EGX70</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>5.24</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1085</v>
+        <v>0.1023</v>
       </c>
       <c r="G15" t="n">
         <v>0.012</v>
@@ -4140,7 +4142,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
-        <v>25225651</v>
+        <v>25243093</v>
       </c>
       <c r="O15" t="n">
         <v>8292933</v>
@@ -4149,17 +4151,15 @@
         <v>0.329</v>
       </c>
       <c r="Q15" t="n">
-        <v>10151793</v>
+        <v>9444708</v>
       </c>
       <c r="R15" t="n">
-        <v>749782</v>
+        <v>1091169</v>
       </c>
       <c r="S15" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="T15" t="n">
-        <v>5.3</v>
-      </c>
+        <v>0.116</v>
+      </c>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="n">
         <v>6.69</v>
       </c>
@@ -4236,17 +4236,17 @@
         </is>
       </c>
       <c r="AP15" t="n">
-        <v>243753346567</v>
+        <v>243747235971</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-60930157</v>
+        <v>-52432335</v>
       </c>
       <c r="AR15" t="n">
-        <v>66.52</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:17</t>
+          <t>2026-09-11 18:20:09</t>
         </is>
       </c>
       <c r="AT15" t="n">
@@ -4325,43 +4325,43 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid</t>
         </is>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>0.4663</v>
       </c>
       <c r="BS15" t="n">
         <v>0</v>
       </c>
       <c r="BT15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ARAB</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EGX70</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>ARAB</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>EGX70</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -4382,7 +4382,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>0.2589</v>
+        <v>0.26</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -4392,28 +4392,28 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
-        <v>295149768</v>
+        <v>296256204</v>
       </c>
       <c r="O16" t="n">
         <v>318346970</v>
       </c>
       <c r="P16" t="n">
-        <v>1.079</v>
+        <v>1.075</v>
       </c>
       <c r="Q16" t="n">
-        <v>170364355</v>
+        <v>153417202</v>
       </c>
       <c r="R16" t="n">
-        <v>163715150</v>
+        <v>176860247</v>
       </c>
       <c r="S16" t="n">
-        <v>0.961</v>
+        <v>1.153</v>
       </c>
       <c r="T16" t="n">
         <v>0.234</v>
       </c>
       <c r="U16" t="n">
-        <v>0.256</v>
+        <v>0.273</v>
       </c>
       <c r="V16" t="n">
         <v>0.2435</v>
@@ -4488,17 +4488,17 @@
         </is>
       </c>
       <c r="AP16" t="n">
-        <v>-19738569955</v>
+        <v>-19703196430</v>
       </c>
       <c r="AQ16" t="n">
-        <v>-364576940</v>
+        <v>-482219532</v>
       </c>
       <c r="AR16" t="n">
-        <v>59.42</v>
+        <v>59.5</v>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:17</t>
+          <t>2026-09-11 18:20:09</t>
         </is>
       </c>
       <c r="AT16" t="n">
@@ -4551,11 +4551,11 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 24.2% above EMA200, MACD below signal (bearish), RSI in healthy bullish zone (56.7), distribution (ADL falling over last 20d); score=37.8/100; entry: enhanced entry at VWMA (overbought (RSI: 56.7)), +0.35% buffer</t>
+          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 24.2% above EMA200, MACD below signal (bearish), RSI in healthy bullish zone (56.7), distribution (ADL falling over last 20d); score=38.3/100; entry: enhanced entry at VWMA (overbought (RSI: 56.7)), +0.35% buffer</t>
         </is>
       </c>
       <c r="BI16" t="n">
-        <v>37.85</v>
+        <v>38.34</v>
       </c>
       <c r="BJ16" t="n">
         <v>10.01</v>
@@ -4567,7 +4567,7 @@
         <v>27.58</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.26</v>
+        <v>0.75</v>
       </c>
       <c r="BN16" t="n">
         <v>0</v>
@@ -4586,41 +4586,41 @@
         </is>
       </c>
       <c r="BR16" t="n">
-        <v>0.4467</v>
+        <v>0.3795</v>
       </c>
       <c r="BS16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>COSG</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EGX70</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>COSG</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>EGX70</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E17" t="n">
         <v>1.9</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0369</v>
+        <v>0.0371</v>
       </c>
       <c r="G17" t="n">
         <v>0.0035</v>
@@ -4634,7 +4634,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>5.915</v>
+        <v>5.9898</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -4646,22 +4646,22 @@
         <v>-0.0638</v>
       </c>
       <c r="N17" t="n">
-        <v>21032524</v>
+        <v>20896580</v>
       </c>
       <c r="O17" t="n">
         <v>6410577</v>
       </c>
       <c r="P17" t="n">
-        <v>0.305</v>
+        <v>0.307</v>
       </c>
       <c r="Q17" t="n">
-        <v>10861141</v>
+        <v>10843858</v>
       </c>
       <c r="R17" t="n">
-        <v>2049495</v>
+        <v>5128462</v>
       </c>
       <c r="S17" t="n">
-        <v>0.189</v>
+        <v>0.473</v>
       </c>
       <c r="T17" t="n">
         <v>1.6</v>
@@ -4742,17 +4742,17 @@
         </is>
       </c>
       <c r="AP17" t="n">
-        <v>3049976913870942</v>
+        <v>3049976917717288</v>
       </c>
       <c r="AQ17" t="n">
-        <v>-13541414</v>
+        <v>-9695068</v>
       </c>
       <c r="AR17" t="n">
         <v>63.46</v>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:17</t>
+          <t>2026-09-11 18:20:09</t>
         </is>
       </c>
       <c r="AT17" t="n">
@@ -4831,19 +4831,19 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="BR17" t="n">
-        <v>0.3382</v>
+        <v>0.3267</v>
       </c>
       <c r="BS17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT17" t="n">
         <v>1</v>
@@ -4852,29 +4852,29 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>POUL</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EGX70</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>POUL</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>EGX70</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E18" t="n">
         <v>39.89</v>
       </c>
       <c r="F18" t="n">
-        <v>0.766</v>
+        <v>0.7789</v>
       </c>
       <c r="G18" t="n">
         <v>0.08890000000000001</v>
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>165.5296</v>
+        <v>169.9351</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -4899,25 +4899,25 @@
         <v>1.91</v>
       </c>
       <c r="M18" t="n">
-        <v>20.4664</v>
+        <v>20.9013</v>
       </c>
       <c r="N18" t="n">
-        <v>1226846</v>
+        <v>1233337</v>
       </c>
       <c r="O18" t="n">
         <v>1974609</v>
       </c>
       <c r="P18" t="n">
-        <v>1.61</v>
+        <v>1.601</v>
       </c>
       <c r="Q18" t="n">
-        <v>257165</v>
+        <v>268651</v>
       </c>
       <c r="R18" t="n">
-        <v>138018</v>
+        <v>883115</v>
       </c>
       <c r="S18" t="n">
-        <v>0.537</v>
+        <v>3.287</v>
       </c>
       <c r="T18" t="n">
         <v>36.97</v>
@@ -4998,17 +4998,17 @@
         </is>
       </c>
       <c r="AP18" t="n">
-        <v>282707011182</v>
+        <v>282706777584</v>
       </c>
       <c r="AQ18" t="n">
-        <v>-449579</v>
+        <v>-728003</v>
       </c>
       <c r="AR18" t="n">
-        <v>61.38</v>
+        <v>61.51</v>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:17</t>
+          <t>2026-09-11 18:20:09</t>
         </is>
       </c>
       <c r="AT18" t="n">
@@ -5061,11 +5061,11 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 20.1% above EMA200, MACD bullish (strength 43%), MACD above zero (confirmed momentum), RSI in healthy bullish zone (57.8), volume 1.61x average, distribution (ADL falling over last 20d); score=51.3/100; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 57.8)), +0.35% buffer</t>
+          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 20.1% above EMA200, MACD bullish (strength 43%), MACD above zero (confirmed momentum), RSI in healthy bullish zone (57.8), volume 1.60x average, buy-volume spike (3.29x), distribution (ADL falling over last 20d); score=63.0/100; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 57.8)), +0.35% buffer</t>
         </is>
       </c>
       <c r="BI18" t="n">
-        <v>51.26</v>
+        <v>63.01</v>
       </c>
       <c r="BJ18" t="n">
         <v>9.6</v>
@@ -5077,7 +5077,7 @@
         <v>27.58</v>
       </c>
       <c r="BM18" t="n">
-        <v>6.15</v>
+        <v>17.9</v>
       </c>
       <c r="BN18" t="n">
         <v>0</v>
@@ -5108,29 +5108,29 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PRCL</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EGX70</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>PRCL</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>EGX70</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E19" t="n">
         <v>32.03</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6217</v>
+        <v>0.6254</v>
       </c>
       <c r="G19" t="n">
         <v>0.09229999999999999</v>
@@ -5152,7 +5152,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
-        <v>1100488</v>
+        <v>1096190</v>
       </c>
       <c r="O19" t="n">
         <v>104355</v>
@@ -5161,16 +5161,16 @@
         <v>0.095</v>
       </c>
       <c r="Q19" t="n">
-        <v>390181</v>
+        <v>390681</v>
       </c>
       <c r="R19" t="n">
-        <v>4447</v>
+        <v>70812</v>
       </c>
       <c r="S19" t="n">
-        <v>0.011</v>
+        <v>0.181</v>
       </c>
       <c r="T19" t="n">
-        <v>30.9</v>
+        <v>32</v>
       </c>
       <c r="U19" t="n">
         <v>36.49</v>
@@ -5248,17 +5248,17 @@
         </is>
       </c>
       <c r="AP19" t="n">
-        <v>14202064588775</v>
+        <v>14202064626045</v>
       </c>
       <c r="AQ19" t="n">
-        <v>506</v>
+        <v>-27791</v>
       </c>
       <c r="AR19" t="n">
-        <v>67.09999999999999</v>
+        <v>67.09</v>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:17</t>
+          <t>2026-09-11 18:20:09</t>
         </is>
       </c>
       <c r="AT19" t="n">
@@ -5306,16 +5306,16 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>EMA50 &gt; EMA200, price above EMA200, Diamond Cross (EMA20&gt;EMA50), price 31.5% above EMA200, MACD below signal (bearish), RSI neutral-firm (44.5), accumulation (ADL rising over last 20d); score=33.3/100; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 44.5)), +0.35% buffer</t>
+          <t>EMA50 &gt; EMA200, price above EMA200, Diamond Cross (EMA20&gt;EMA50), price 31.5% above EMA200, MACD below signal (bearish), RSI neutral-firm (44.5), distribution (ADL falling over last 20d), price near support; score=40.9/100; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 44.5)), +0.35% buffer</t>
         </is>
       </c>
       <c r="BI19" t="n">
-        <v>33.26</v>
+        <v>40.95</v>
       </c>
       <c r="BJ19" t="n">
         <v>8.07</v>
@@ -5330,26 +5330,26 @@
         <v>0</v>
       </c>
       <c r="BN19" t="n">
-        <v>8.65</v>
+        <v>0</v>
       </c>
       <c r="BO19" t="n">
-        <v>0</v>
+        <v>16.33</v>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="BR19" t="n">
-        <v>0</v>
+        <v>0.363</v>
       </c>
       <c r="BS19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT19" t="n">
         <v>0</v>
@@ -5358,29 +5358,29 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ETRS</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EGX70</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ETRS</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>EGX70</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E20" t="n">
         <v>11.25</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2193</v>
+        <v>0.2197</v>
       </c>
       <c r="G20" t="n">
         <v>0.0238</v>
@@ -5390,11 +5390,11 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>11.1081</v>
+        <v>11.453</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
-        <v>4394011</v>
+        <v>4391535</v>
       </c>
       <c r="O20" t="n">
         <v>502350</v>
@@ -5413,13 +5413,13 @@
         <v>0.114</v>
       </c>
       <c r="Q20" t="n">
-        <v>1143185</v>
+        <v>1145269</v>
       </c>
       <c r="R20" t="n">
-        <v>104997</v>
+        <v>390717</v>
       </c>
       <c r="S20" t="n">
-        <v>0.092</v>
+        <v>0.341</v>
       </c>
       <c r="T20" t="n">
         <v>10.7</v>
@@ -5500,17 +5500,17 @@
         </is>
       </c>
       <c r="AP20" t="n">
-        <v>1899888876957</v>
+        <v>1899887912587</v>
       </c>
       <c r="AQ20" t="n">
-        <v>9408865</v>
+        <v>7517778</v>
       </c>
       <c r="AR20" t="n">
         <v>66.98999999999999</v>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:17</t>
+          <t>2026-09-11 18:20:09</t>
         </is>
       </c>
       <c r="AT20" t="n">
@@ -5598,7 +5598,7 @@
         </is>
       </c>
       <c r="BR20" t="n">
-        <v>0.3323</v>
+        <v>0.3247</v>
       </c>
       <c r="BS20" t="n">
         <v>0</v>
@@ -5610,29 +5610,29 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>OBRI</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EGX70</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>OBRI</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>EGX70</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E21" t="n">
         <v>32.85</v>
       </c>
       <c r="F21" t="n">
-        <v>0.646</v>
+        <v>0.6414</v>
       </c>
       <c r="G21" t="n">
         <v>0.0613</v>
@@ -5646,7 +5646,7 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>33.7683</v>
+        <v>33.6408</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>2.0553</v>
       </c>
       <c r="N21" t="n">
-        <v>665330</v>
+        <v>665113</v>
       </c>
       <c r="O21" t="n">
         <v>332165</v>
@@ -5669,19 +5669,19 @@
         <v>0.499</v>
       </c>
       <c r="Q21" t="n">
-        <v>226782</v>
+        <v>219202</v>
       </c>
       <c r="R21" t="n">
-        <v>293479</v>
+        <v>249946</v>
       </c>
       <c r="S21" t="n">
-        <v>1.294</v>
+        <v>1.14</v>
       </c>
       <c r="T21" t="n">
         <v>31.81</v>
       </c>
       <c r="U21" t="n">
-        <v>34.97</v>
+        <v>34.95</v>
       </c>
       <c r="V21" t="n">
         <v>33.9434</v>
@@ -5756,17 +5756,17 @@
         </is>
       </c>
       <c r="AP21" t="n">
-        <v>137558919158317</v>
+        <v>137558919326044</v>
       </c>
       <c r="AQ21" t="n">
-        <v>-1530890</v>
+        <v>-1392532</v>
       </c>
       <c r="AR21" t="n">
-        <v>63.73</v>
+        <v>63.65</v>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:17</t>
+          <t>2026-09-11 18:20:09</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -5797,11 +5797,11 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>EMA50 &gt; EMA200, price above EMA200, price 3.3% above EMA200, MACD bullish (strength 37%), RSI neutral-firm (46.2), distribution (ADL falling over last 20d), Death Cross (SMA50&lt;SMA200) overrides score to Avoid; score=27.9/100; entry: no entry in bearish/unknown regime</t>
+          <t>EMA50 &gt; EMA200, price above EMA200, price 3.3% above EMA200, MACD bullish (strength 37%), RSI neutral-firm (46.2), distribution (ADL falling over last 20d), Death Cross (SMA50&lt;SMA200) overrides score to Avoid; score=27.4/100; entry: no entry in bearish/unknown regime</t>
         </is>
       </c>
       <c r="BI21" t="n">
-        <v>27.86</v>
+        <v>27.35</v>
       </c>
       <c r="BJ21" t="n">
         <v>3.87</v>
@@ -5813,7 +5813,7 @@
         <v>16.55</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.97</v>
+        <v>0.46</v>
       </c>
       <c r="BN21" t="n">
         <v>0</v>
@@ -5832,41 +5832,41 @@
         </is>
       </c>
       <c r="BR21" t="n">
-        <v>0.3698</v>
+        <v>0.3594</v>
       </c>
       <c r="BS21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NIPH</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EGX70</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>NIPH</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>EGX70</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E22" t="n">
         <v>337.99</v>
       </c>
       <c r="F22" t="n">
-        <v>6.57</v>
+        <v>6.5997</v>
       </c>
       <c r="G22" t="n">
         <v>0.4421</v>
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>191.4065</v>
+        <v>193.2225</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -5888,28 +5888,28 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>14.57</v>
+        <v>14.54</v>
       </c>
       <c r="M22" t="n">
-        <v>22.9958</v>
+        <v>23.2495</v>
       </c>
       <c r="N22" t="n">
-        <v>421369</v>
+        <v>419766</v>
       </c>
       <c r="O22" t="n">
         <v>335965</v>
       </c>
       <c r="P22" t="n">
-        <v>0.797</v>
+        <v>0.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>429937</v>
+        <v>433855</v>
       </c>
       <c r="R22" t="n">
-        <v>35573</v>
+        <v>209399</v>
       </c>
       <c r="S22" t="n">
-        <v>0.083</v>
+        <v>0.483</v>
       </c>
       <c r="T22" t="n">
         <v>330</v>
@@ -5990,17 +5990,17 @@
         </is>
       </c>
       <c r="AP22" t="n">
-        <v>931170725796177</v>
+        <v>931170803836016</v>
       </c>
       <c r="AQ22" t="n">
-        <v>-3588381</v>
+        <v>-2906031</v>
       </c>
       <c r="AR22" t="n">
-        <v>62.52</v>
+        <v>62.72</v>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:17</t>
+          <t>2026-09-11 18:20:09</t>
         </is>
       </c>
       <c r="AT22" t="n">
@@ -6079,19 +6079,19 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="BR22" t="n">
-        <v>0.3253</v>
+        <v>0</v>
       </c>
       <c r="BS22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT22" t="n">
         <v>0</v>
@@ -6100,29 +6100,29 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SWDY</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EGX70</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>SWDY</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>EGX70</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E23" t="n">
         <v>127.5</v>
       </c>
       <c r="F23" t="n">
-        <v>2.5672</v>
+        <v>2.4896</v>
       </c>
       <c r="G23" t="n">
         <v>0.2765</v>
@@ -6136,7 +6136,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>187.4849</v>
+        <v>183.4171</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -6147,25 +6147,25 @@
         <v>6.27</v>
       </c>
       <c r="M23" t="n">
-        <v>20.888</v>
+        <v>20.3455</v>
       </c>
       <c r="N23" t="n">
-        <v>343360</v>
+        <v>346853</v>
       </c>
       <c r="O23" t="n">
         <v>974004</v>
       </c>
       <c r="P23" t="n">
-        <v>2.837</v>
+        <v>2.808</v>
       </c>
       <c r="Q23" t="n">
-        <v>285951</v>
+        <v>286417</v>
       </c>
       <c r="R23" t="n">
-        <v>259897</v>
+        <v>80347</v>
       </c>
       <c r="S23" t="n">
-        <v>0.909</v>
+        <v>0.281</v>
       </c>
       <c r="T23" t="n">
         <v>91.8</v>
@@ -6246,17 +6246,17 @@
         </is>
       </c>
       <c r="AP23" t="n">
-        <v>-127851868</v>
+        <v>-128665178</v>
       </c>
       <c r="AQ23" t="n">
-        <v>-2762028</v>
+        <v>-2945970</v>
       </c>
       <c r="AR23" t="n">
-        <v>59.67</v>
+        <v>59.6</v>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:17</t>
+          <t>2026-09-11 18:20:09</t>
         </is>
       </c>
       <c r="AT23" t="n">
@@ -6309,11 +6309,11 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 38.1% above EMA200, MACD below signal (bearish), RSI in healthy bullish zone (58.8), volume 2.84x average, distribution (ADL falling over last 20d); score=54.4/100; entry: enhanced entry at VWMA (overbought (RSI: 58.8)), +0.35% buffer</t>
+          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 38.1% above EMA200, MACD below signal (bearish), RSI in healthy bullish zone (58.8), volume 2.81x average, distribution (ADL falling over last 20d); score=54.2/100; entry: enhanced entry at VWMA (overbought (RSI: 58.8)), +0.35% buffer</t>
         </is>
       </c>
       <c r="BI23" t="n">
-        <v>54.39</v>
+        <v>54.19</v>
       </c>
       <c r="BJ23" t="n">
         <v>10.09</v>
@@ -6325,7 +6325,7 @@
         <v>27.58</v>
       </c>
       <c r="BM23" t="n">
-        <v>16.73</v>
+        <v>16.52</v>
       </c>
       <c r="BN23" t="n">
         <v>0</v>
@@ -6356,29 +6356,29 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ENGC</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EGX70</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>ENGC</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>EGX70</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E24" t="n">
         <v>44.33</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8672</v>
+        <v>0.8656</v>
       </c>
       <c r="G24" t="n">
         <v>0.1033</v>
@@ -6392,7 +6392,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>109.0314</v>
+        <v>95.1378</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -6400,28 +6400,28 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.71</v>
+        <v>4.39</v>
       </c>
       <c r="M24" t="n">
-        <v>11.9235</v>
+        <v>10.1043</v>
       </c>
       <c r="N24" t="n">
-        <v>415464</v>
+        <v>413850</v>
       </c>
       <c r="O24" t="n">
         <v>128206</v>
       </c>
       <c r="P24" t="n">
-        <v>0.309</v>
+        <v>0.31</v>
       </c>
       <c r="Q24" t="n">
-        <v>307897</v>
+        <v>252111</v>
       </c>
       <c r="R24" t="n">
-        <v>33107</v>
+        <v>53206</v>
       </c>
       <c r="S24" t="n">
-        <v>0.108</v>
+        <v>0.211</v>
       </c>
       <c r="T24" t="n">
         <v>41.8</v>
@@ -6502,17 +6502,17 @@
         </is>
       </c>
       <c r="AP24" t="n">
-        <v>-25967529310787</v>
+        <v>-25967528864752</v>
       </c>
       <c r="AQ24" t="n">
-        <v>-1164596</v>
+        <v>-1175555</v>
       </c>
       <c r="AR24" t="n">
-        <v>68.01000000000001</v>
+        <v>67.94</v>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:17</t>
+          <t>2026-09-11 18:20:09</t>
         </is>
       </c>
       <c r="AT24" t="n">
@@ -6612,29 +6612,29 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ZEOT</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EGX70</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>ZEOT</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>EGX70</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E25" t="n">
         <v>14</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2744</v>
+        <v>0.2734</v>
       </c>
       <c r="G25" t="n">
         <v>0.0323</v>
@@ -6648,7 +6648,7 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>14.1168</v>
+        <v>14.1549</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>2807371</v>
+        <v>2802042</v>
       </c>
       <c r="O25" t="n">
         <v>149375</v>
@@ -6667,17 +6667,17 @@
         <v>0.053</v>
       </c>
       <c r="Q25" t="n">
-        <v>687472</v>
+        <v>662741</v>
       </c>
       <c r="R25" t="n">
-        <v>134702</v>
+        <v>91923</v>
       </c>
       <c r="S25" t="n">
-        <v>0.196</v>
+        <v>0.139</v>
       </c>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="n">
-        <v>14.99</v>
+        <v>14.85</v>
       </c>
       <c r="V25" t="n">
         <v>12.7476</v>
@@ -6752,17 +6752,17 @@
         </is>
       </c>
       <c r="AP25" t="n">
-        <v>3322247492127</v>
+        <v>3322247140936</v>
       </c>
       <c r="AQ25" t="n">
-        <v>-4430627</v>
+        <v>-4193070</v>
       </c>
       <c r="AR25" t="n">
-        <v>68.34</v>
+        <v>68.27</v>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:17</t>
+          <t>2026-09-11 18:20:09</t>
         </is>
       </c>
       <c r="AT25" t="n">
@@ -6862,29 +6862,29 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BIOC</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EGX70</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>BIOC</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>EGX70</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E26" t="n">
         <v>289.1</v>
       </c>
       <c r="F26" t="n">
-        <v>5.9816</v>
+        <v>5.6451</v>
       </c>
       <c r="G26" t="n">
         <v>0.2954</v>
@@ -6898,7 +6898,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>9130.768899999999</v>
+        <v>8226.6111</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -6906,28 +6906,28 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="M26" t="n">
-        <v>1445.0017</v>
+        <v>1298.3109</v>
       </c>
       <c r="N26" t="n">
-        <v>183792</v>
+        <v>183381</v>
       </c>
       <c r="O26" t="n">
         <v>195718</v>
       </c>
       <c r="P26" t="n">
-        <v>1.065</v>
+        <v>1.067</v>
       </c>
       <c r="Q26" t="n">
-        <v>367583</v>
+        <v>368324</v>
       </c>
       <c r="R26" t="n">
-        <v>24017</v>
+        <v>33435</v>
       </c>
       <c r="S26" t="n">
-        <v>0.065</v>
+        <v>0.091</v>
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="n">
@@ -7006,17 +7006,17 @@
         </is>
       </c>
       <c r="AP26" t="n">
-        <v>99374616540282</v>
+        <v>99374626378795</v>
       </c>
       <c r="AQ26" t="n">
-        <v>-3080000</v>
+        <v>-3334866</v>
       </c>
       <c r="AR26" t="n">
-        <v>60.45</v>
+        <v>60.12</v>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:17</t>
+          <t>2026-09-11 18:20:09</t>
         </is>
       </c>
       <c r="AT26" t="n">
@@ -7085,7 +7085,7 @@
         <v>11.03</v>
       </c>
       <c r="BM26" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="BN26" t="n">
         <v>0</v>
@@ -7116,29 +7116,29 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>IFAP</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EGX70</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>IFAP</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>EGX70</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E27" t="n">
         <v>20.9</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4144</v>
+        <v>0.4081</v>
       </c>
       <c r="G27" t="n">
         <v>0.0403</v>
@@ -7152,7 +7152,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>21.3852</v>
+        <v>21.6054</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>752581</v>
+        <v>752849</v>
       </c>
       <c r="O27" t="n">
         <v>657962</v>
@@ -7171,13 +7171,13 @@
         <v>0.874</v>
       </c>
       <c r="Q27" t="n">
-        <v>478813</v>
+        <v>486752</v>
       </c>
       <c r="R27" t="n">
-        <v>165790</v>
+        <v>396866</v>
       </c>
       <c r="S27" t="n">
-        <v>0.346</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="T27" t="n">
         <v>20.2</v>
@@ -7258,17 +7258,17 @@
         </is>
       </c>
       <c r="AP27" t="n">
-        <v>-363743020602</v>
+        <v>-363742884833</v>
       </c>
       <c r="AQ27" t="n">
-        <v>-8393780</v>
+        <v>-8258011</v>
       </c>
       <c r="AR27" t="n">
-        <v>63.77</v>
+        <v>63.71</v>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:17</t>
+          <t>2026-09-11 18:20:09</t>
         </is>
       </c>
       <c r="AT27" t="n">
@@ -7347,50 +7347,50 @@
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="BR27" t="n">
-        <v>0.5012</v>
+        <v>0.4935</v>
       </c>
       <c r="BS27" t="n">
         <v>1</v>
       </c>
       <c r="BT27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ICFC</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EGX70</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>ICFC</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>EGX70</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E28" t="n">
         <v>23.6</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4697</v>
+        <v>0.4608</v>
       </c>
       <c r="G28" t="n">
         <v>0.0519</v>
@@ -7404,7 +7404,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>25.5551</v>
+        <v>24.9808</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -7414,22 +7414,22 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>1198603</v>
+        <v>1199836</v>
       </c>
       <c r="O28" t="n">
         <v>530891</v>
       </c>
       <c r="P28" t="n">
-        <v>0.443</v>
+        <v>0.442</v>
       </c>
       <c r="Q28" t="n">
-        <v>1350358</v>
+        <v>1352754</v>
       </c>
       <c r="R28" t="n">
-        <v>1871949</v>
+        <v>268806</v>
       </c>
       <c r="S28" t="n">
-        <v>1.386</v>
+        <v>0.199</v>
       </c>
       <c r="T28" t="n">
         <v>15.33</v>
@@ -7508,17 +7508,17 @@
         </is>
       </c>
       <c r="AP28" t="n">
-        <v>402016798551646</v>
+        <v>402016798558366</v>
       </c>
       <c r="AQ28" t="n">
-        <v>14222447</v>
+        <v>14030287</v>
       </c>
       <c r="AR28" t="n">
-        <v>64.67</v>
+        <v>64.72</v>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:17</t>
+          <t>2026-09-11 18:20:09</t>
         </is>
       </c>
       <c r="AT28" t="n">
@@ -7571,11 +7571,11 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 46.0% above EMA200, MACD bullish (strength 1%), MACD above zero (confirmed momentum), RSI in healthy bullish zone (65.4), accumulation (ADL rising over last 20d); score=52.9/100; entry: enhanced entry at VWMA (overbought (RSI: 65.4)), +0.35% buffer</t>
+          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 46.0% above EMA200, MACD bullish (strength 1%), MACD above zero (confirmed momentum), RSI in healthy bullish zone (65.4), accumulation (ADL rising over last 20d); score=51.6/100; entry: enhanced entry at VWMA (overbought (RSI: 65.4)), +0.35% buffer</t>
         </is>
       </c>
       <c r="BI28" t="n">
-        <v>52.88</v>
+        <v>51.61</v>
       </c>
       <c r="BJ28" t="n">
         <v>10.09</v>
@@ -7587,7 +7587,7 @@
         <v>27.58</v>
       </c>
       <c r="BM28" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BN28" t="n">
         <v>8.65</v>
@@ -7618,29 +7618,29 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ISMA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EGX70</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>ISMA</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>EGX70</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E29" t="n">
         <v>32.25</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6301</v>
+        <v>0.6297</v>
       </c>
       <c r="G29" t="n">
         <v>0.0804</v>
@@ -7662,22 +7662,22 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>1307236</v>
+        <v>1309493</v>
       </c>
       <c r="O29" t="n">
         <v>2690211</v>
       </c>
       <c r="P29" t="n">
-        <v>2.058</v>
+        <v>2.054</v>
       </c>
       <c r="Q29" t="n">
-        <v>420247</v>
+        <v>442691</v>
       </c>
       <c r="R29" t="n">
-        <v>101312</v>
+        <v>1120921</v>
       </c>
       <c r="S29" t="n">
-        <v>0.241</v>
+        <v>2.532</v>
       </c>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="n">
@@ -7756,17 +7756,17 @@
         </is>
       </c>
       <c r="AP29" t="n">
-        <v>2766852029555</v>
+        <v>2766851581187</v>
       </c>
       <c r="AQ29" t="n">
-        <v>829768</v>
+        <v>38759</v>
       </c>
       <c r="AR29" t="n">
-        <v>67.64</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:17</t>
+          <t>2026-09-11 18:20:09</t>
         </is>
       </c>
       <c r="AT29" t="n">
@@ -7814,16 +7814,16 @@
       </c>
       <c r="BG29" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 40.0% above EMA200, MACD below signal (bearish), RSI neutral-firm (44.9), volume 2.06x average, accumulation (ADL rising over last 20d); score=46.4/100; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 44.9)), +0.35% buffer</t>
+          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 40.0% above EMA200, MACD below signal (bearish), RSI neutral-firm (44.9), volume 2.05x average, buy-volume spike (2.53x), accumulation (ADL rising over last 20d); score=53.2/100; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 44.9)), +0.35% buffer</t>
         </is>
       </c>
       <c r="BI29" t="n">
-        <v>46.44</v>
+        <v>53.18</v>
       </c>
       <c r="BJ29" t="n">
         <v>10.09</v>
@@ -7835,7 +7835,7 @@
         <v>16.55</v>
       </c>
       <c r="BM29" t="n">
-        <v>11.15</v>
+        <v>17.9</v>
       </c>
       <c r="BN29" t="n">
         <v>8.65</v>
@@ -7854,7 +7854,7 @@
         </is>
       </c>
       <c r="BR29" t="n">
-        <v>0.6422</v>
+        <v>0.5767</v>
       </c>
       <c r="BS29" t="n">
         <v>0</v>
@@ -7866,29 +7866,29 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>LCSW</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EGX70</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>LCSW</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>EGX70</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E30" t="n">
         <v>34.8</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6741</v>
+        <v>0.6795</v>
       </c>
       <c r="G30" t="n">
         <v>0.1136</v>
@@ -7902,7 +7902,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>43.2868</v>
+        <v>43.6834</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -7913,25 +7913,25 @@
         <v>10.21</v>
       </c>
       <c r="M30" t="n">
-        <v>3.3649</v>
+        <v>3.407</v>
       </c>
       <c r="N30" t="n">
-        <v>825238</v>
+        <v>826434</v>
       </c>
       <c r="O30" t="n">
         <v>610268</v>
       </c>
       <c r="P30" t="n">
-        <v>0.74</v>
+        <v>0.738</v>
       </c>
       <c r="Q30" t="n">
-        <v>534051</v>
+        <v>546644</v>
       </c>
       <c r="R30" t="n">
-        <v>84006</v>
+        <v>528899</v>
       </c>
       <c r="S30" t="n">
-        <v>0.157</v>
+        <v>0.968</v>
       </c>
       <c r="T30" t="n">
         <v>33.45</v>
@@ -8012,17 +8012,17 @@
         </is>
       </c>
       <c r="AP30" t="n">
-        <v>263836104077935</v>
+        <v>263836104525465</v>
       </c>
       <c r="AQ30" t="n">
-        <v>-924505</v>
+        <v>251509</v>
       </c>
       <c r="AR30" t="n">
-        <v>65.15000000000001</v>
+        <v>65.08</v>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:17</t>
+          <t>2026-09-11 18:20:09</t>
         </is>
       </c>
       <c r="AT30" t="n">
@@ -8070,16 +8070,16 @@
       </c>
       <c r="BG30" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 19.6% above EMA200, MACD below signal (bearish), RSI in healthy bullish zone (52.5), distribution (ADL falling over last 20d); score=37.1/100; entry: enhanced entry at VWMA (overbought (RSI: 52.5)), +0.35% buffer</t>
+          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 19.6% above EMA200, MACD below signal (bearish), RSI in healthy bullish zone (52.5), accumulation (ADL rising over last 20d); score=45.8/100; entry: enhanced entry at VWMA (overbought (RSI: 52.5)), +0.35% buffer</t>
         </is>
       </c>
       <c r="BI30" t="n">
-        <v>37.12</v>
+        <v>45.76</v>
       </c>
       <c r="BJ30" t="n">
         <v>9.539999999999999</v>
@@ -8094,7 +8094,7 @@
         <v>0</v>
       </c>
       <c r="BN30" t="n">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="BO30" t="n">
         <v>0</v>
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="BR30" t="n">
-        <v>0.3245</v>
+        <v>0.3551</v>
       </c>
       <c r="BS30" t="n">
         <v>1</v>
@@ -8122,29 +8122,29 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MPCO</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EGX70</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>MPCO</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>EGX70</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E31" t="n">
         <v>2.6</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0449</v>
+        <v>0.0508</v>
       </c>
       <c r="G31" t="n">
         <v>0.0055</v>
@@ -8166,29 +8166,27 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>38002472</v>
+        <v>38935951</v>
       </c>
       <c r="O31" t="n">
         <v>238639807</v>
       </c>
       <c r="P31" t="n">
-        <v>6.28</v>
+        <v>6.129</v>
       </c>
       <c r="Q31" t="n">
-        <v>18579954</v>
+        <v>22676206</v>
       </c>
       <c r="R31" t="n">
-        <v>39697272</v>
+        <v>172042593</v>
       </c>
       <c r="S31" t="n">
-        <v>2.137</v>
+        <v>7.587</v>
       </c>
       <c r="T31" t="n">
         <v>2.07</v>
       </c>
-      <c r="U31" t="n">
-        <v>2.38</v>
-      </c>
+      <c r="U31" t="inlineStr"/>
       <c r="V31" t="n">
         <v>2.0452</v>
       </c>
@@ -8262,17 +8260,17 @@
         </is>
       </c>
       <c r="AP31" t="n">
-        <v>5163842389317</v>
+        <v>5163947834696</v>
       </c>
       <c r="AQ31" t="n">
-        <v>-114144212</v>
+        <v>28928441</v>
       </c>
       <c r="AR31" t="n">
-        <v>65.73999999999999</v>
+        <v>66.36</v>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:17</t>
+          <t>2026-09-11 18:20:09</t>
         </is>
       </c>
       <c r="AT31" t="n">
@@ -8293,11 +8291,11 @@
         <v>3.0733</v>
       </c>
       <c r="AY31" t="n">
-        <v>2.8669</v>
+        <v>2.9749</v>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 2.6; TP2: Classic R3 at 3.07; TP3: ATR target (full) at 2.87</t>
+          <t>TP1: Classic R2 at 2.6; TP2: Classic R3 at 3.07; TP3: ATR target (full) at 2.97</t>
         </is>
       </c>
       <c r="BA31" t="n">
@@ -8307,7 +8305,7 @@
         <v>2.99</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.15</v>
+        <v>2.59</v>
       </c>
       <c r="BD31" t="n">
         <v>11.34</v>
@@ -8316,20 +8314,20 @@
         <v>31.44</v>
       </c>
       <c r="BF31" t="n">
-        <v>22.62</v>
+        <v>27.23</v>
       </c>
       <c r="BG31" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 47.5% above EMA200, MACD bullish (strength 27%), MACD above zero (confirmed momentum), RSI mildly overbought (72.0) (strong trend maintained), volume 6.28x average, buy-volume spike (2.14x), distribution (ADL falling over last 20d); score=48.7/100; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 72.0)), +0.35% buffer</t>
+          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 47.5% above EMA200, MACD bullish (strength 27%), MACD above zero (confirmed momentum), RSI mildly overbought (72.0) (strong trend maintained), volume 6.13x average, buy-volume spike (7.59x), accumulation (ADL rising over last 20d); score=57.4/100; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 72.0)), +0.35% buffer</t>
         </is>
       </c>
       <c r="BI31" t="n">
-        <v>48.71</v>
+        <v>57.36</v>
       </c>
       <c r="BJ31" t="n">
         <v>10.09</v>
@@ -8344,26 +8342,26 @@
         <v>17.9</v>
       </c>
       <c r="BN31" t="n">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="BO31" t="n">
         <v>0</v>
       </c>
       <c r="BP31" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="BR31" t="n">
-        <v>0</v>
+        <v>0.3477</v>
       </c>
       <c r="BS31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT31" t="n">
         <v>0</v>
@@ -8372,35 +8370,35 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ATQA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EGX70</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>ATQA</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>EGX70</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E32" t="n">
         <v>13.08</v>
       </c>
       <c r="F32" t="n">
-        <v>0.255</v>
+        <v>0.2554</v>
       </c>
       <c r="G32" t="n">
         <v>0.0137</v>
       </c>
       <c r="H32" t="n">
-        <v>0.255</v>
+        <v>0.2554</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -8416,22 +8414,22 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>5256080</v>
+        <v>5273326</v>
       </c>
       <c r="O32" t="n">
         <v>9725847</v>
       </c>
       <c r="P32" t="n">
-        <v>1.85</v>
+        <v>1.844</v>
       </c>
       <c r="Q32" t="n">
-        <v>3477028</v>
+        <v>3617508</v>
       </c>
       <c r="R32" t="n">
-        <v>7414946</v>
+        <v>7059081</v>
       </c>
       <c r="S32" t="n">
-        <v>2.133</v>
+        <v>1.951</v>
       </c>
       <c r="T32" t="n">
         <v>10.8</v>
@@ -8510,17 +8508,17 @@
         </is>
       </c>
       <c r="AP32" t="n">
-        <v>10488201483224</v>
+        <v>10488205875538</v>
       </c>
       <c r="AQ32" t="n">
-        <v>42626369</v>
+        <v>45762943</v>
       </c>
       <c r="AR32" t="n">
-        <v>64.86</v>
+        <v>64.95</v>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:17</t>
+          <t>2026-09-11 18:20:09</t>
         </is>
       </c>
       <c r="AT32" t="n">
@@ -8573,11 +8571,11 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 31.4% above EMA200, MACD bullish (strength 16%), MACD above zero (confirmed momentum), RSI overbought (76.8) (strong trend, penalty reduced), volume 1.85x average, buy-volume spike (2.13x), accumulation (ADL rising over last 20d); score=52.5/100; entry: enhanced entry at Parabolic SAR (overbought (RSI: 76.8)), +0.35% buffer</t>
+          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 31.4% above EMA200, MACD bullish (strength 16%), MACD above zero (confirmed momentum), RSI overbought (76.8) (strong trend, penalty reduced), volume 1.84x average, buy-volume spike (1.95x), accumulation (ADL rising over last 20d); score=52.4/100; entry: enhanced entry at Parabolic SAR (overbought (RSI: 76.8)), +0.35% buffer</t>
         </is>
       </c>
       <c r="BI32" t="n">
-        <v>52.5</v>
+        <v>52.37</v>
       </c>
       <c r="BJ32" t="n">
         <v>10.09</v>
@@ -8589,7 +8587,7 @@
         <v>9.65</v>
       </c>
       <c r="BM32" t="n">
-        <v>17.9</v>
+        <v>17.77</v>
       </c>
       <c r="BN32" t="n">
         <v>8.65</v>
@@ -8608,7 +8606,7 @@
         </is>
       </c>
       <c r="BR32" t="n">
-        <v>0.3247</v>
+        <v>0.4027</v>
       </c>
       <c r="BS32" t="n">
         <v>0</v>
@@ -8620,29 +8618,29 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>MTIE</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EGX70</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>MTIE</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>EGX70</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E33" t="n">
         <v>8.6</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1675</v>
+        <v>0.1679</v>
       </c>
       <c r="G33" t="n">
         <v>0.06519999999999999</v>
@@ -8656,7 +8654,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>5.0685</v>
+        <v>5.0957</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -8667,10 +8665,10 @@
         <v>19.02</v>
       </c>
       <c r="M33" t="n">
-        <v>0.449</v>
+        <v>0.4521</v>
       </c>
       <c r="N33" t="n">
-        <v>3096817</v>
+        <v>3096201</v>
       </c>
       <c r="O33" t="n">
         <v>1421022</v>
@@ -8679,19 +8677,19 @@
         <v>0.459</v>
       </c>
       <c r="Q33" t="n">
-        <v>2344925</v>
+        <v>2230460</v>
       </c>
       <c r="R33" t="n">
-        <v>177894</v>
+        <v>1065769</v>
       </c>
       <c r="S33" t="n">
-        <v>0.076</v>
+        <v>0.478</v>
       </c>
       <c r="T33" t="n">
         <v>8.25</v>
       </c>
       <c r="U33" t="n">
-        <v>9.82</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="V33" t="n">
         <v>8.4221</v>
@@ -8766,17 +8764,17 @@
         </is>
       </c>
       <c r="AP33" t="n">
-        <v>275057631823688</v>
+        <v>275057632534205</v>
       </c>
       <c r="AQ33" t="n">
-        <v>-17766709</v>
+        <v>-23425131</v>
       </c>
       <c r="AR33" t="n">
-        <v>61.5</v>
+        <v>61.52</v>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:17</t>
+          <t>2026-09-11 18:20:09</t>
         </is>
       </c>
       <c r="AT33" t="n">
@@ -8864,7 +8862,7 @@
         </is>
       </c>
       <c r="BR33" t="n">
-        <v>0.3958</v>
+        <v>0.3892</v>
       </c>
       <c r="BS33" t="n">
         <v>1</v>
@@ -8876,29 +8874,29 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>RACC</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EGX70</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>RACC</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>EGX70</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E34" t="n">
         <v>9.9</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1967</v>
+        <v>0.1933</v>
       </c>
       <c r="G34" t="n">
         <v>0.0602</v>
@@ -8912,7 +8910,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>10.1029</v>
+        <v>10.1032</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -8922,7 +8920,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>2501764</v>
+        <v>2501500</v>
       </c>
       <c r="O34" t="n">
         <v>912679</v>
@@ -8931,13 +8929,13 @@
         <v>0.365</v>
       </c>
       <c r="Q34" t="n">
-        <v>1062353</v>
+        <v>1044687</v>
       </c>
       <c r="R34" t="n">
-        <v>33781</v>
+        <v>165941</v>
       </c>
       <c r="S34" t="n">
-        <v>0.032</v>
+        <v>0.159</v>
       </c>
       <c r="T34" t="n">
         <v>9.800000000000001</v>
@@ -9018,17 +9016,17 @@
         </is>
       </c>
       <c r="AP34" t="n">
-        <v>211888533454791</v>
+        <v>211888532882075</v>
       </c>
       <c r="AQ34" t="n">
-        <v>-5365869</v>
+        <v>-6545956</v>
       </c>
       <c r="AR34" t="n">
-        <v>60.59</v>
+        <v>60.54</v>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:17</t>
+          <t>2026-09-11 18:20:09</t>
         </is>
       </c>
       <c r="AT34" t="n">
@@ -9107,19 +9105,19 @@
       </c>
       <c r="BP34" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="BQ34" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="BR34" t="n">
-        <v>0.384</v>
+        <v>0</v>
       </c>
       <c r="BS34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT34" t="n">
         <v>0</v>
@@ -9128,29 +9126,29 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SKPC</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EGX70</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>SKPC</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>EGX70</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E35" t="n">
         <v>18.5</v>
       </c>
       <c r="F35" t="n">
-        <v>0.3634</v>
+        <v>0.3612</v>
       </c>
       <c r="G35" t="n">
         <v>0.1853</v>
@@ -9164,7 +9162,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>3.4982</v>
+        <v>3.4945</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -9175,25 +9173,25 @@
         <v>104.96</v>
       </c>
       <c r="M35" t="n">
-        <v>0.1765</v>
+        <v>0.1763</v>
       </c>
       <c r="N35" t="n">
-        <v>3358005</v>
+        <v>3371685</v>
       </c>
       <c r="O35" t="n">
         <v>4264833</v>
       </c>
       <c r="P35" t="n">
-        <v>1.27</v>
+        <v>1.265</v>
       </c>
       <c r="Q35" t="n">
-        <v>2197681</v>
+        <v>2199453</v>
       </c>
       <c r="R35" t="n">
-        <v>1282419</v>
+        <v>793456</v>
       </c>
       <c r="S35" t="n">
-        <v>0.584</v>
+        <v>0.361</v>
       </c>
       <c r="T35" t="n">
         <v>15.61</v>
@@ -9272,17 +9270,17 @@
         </is>
       </c>
       <c r="AP35" t="n">
-        <v>-188131207</v>
+        <v>-190809128</v>
       </c>
       <c r="AQ35" t="n">
-        <v>-794612</v>
+        <v>-4119049</v>
       </c>
       <c r="AR35" t="n">
-        <v>61.55</v>
+        <v>61.48</v>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:17</t>
+          <t>2026-09-11 18:20:09</t>
         </is>
       </c>
       <c r="AT35" t="n">
@@ -9339,7 +9337,7 @@
         </is>
       </c>
       <c r="BI35" t="n">
-        <v>43.01</v>
+        <v>42.99</v>
       </c>
       <c r="BJ35" t="n">
         <v>8.66</v>
@@ -9351,7 +9349,7 @@
         <v>27.58</v>
       </c>
       <c r="BM35" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="BN35" t="n">
         <v>0</v>
@@ -9370,7 +9368,7 @@
         </is>
       </c>
       <c r="BR35" t="n">
-        <v>0.417</v>
+        <v>0.3691</v>
       </c>
       <c r="BS35" t="n">
         <v>1</v>
@@ -9382,29 +9380,29 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SCEM</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EGX70</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>SCEM</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>EGX70</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E36" t="n">
         <v>100.29</v>
       </c>
       <c r="F36" t="n">
-        <v>1.9612</v>
+        <v>1.9583</v>
       </c>
       <c r="G36" t="n">
         <v>0.1693</v>
@@ -9418,7 +9416,7 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>733.7138</v>
+        <v>735.6604</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -9429,10 +9427,10 @@
         <v>0.99</v>
       </c>
       <c r="M36" t="n">
-        <v>101.4793</v>
+        <v>101.7736</v>
       </c>
       <c r="N36" t="n">
-        <v>776561</v>
+        <v>776949</v>
       </c>
       <c r="O36" t="n">
         <v>454347</v>
@@ -9441,19 +9439,19 @@
         <v>0.585</v>
       </c>
       <c r="Q36" t="n">
-        <v>729766</v>
+        <v>732486</v>
       </c>
       <c r="R36" t="n">
-        <v>149485</v>
+        <v>158333</v>
       </c>
       <c r="S36" t="n">
-        <v>0.205</v>
+        <v>0.216</v>
       </c>
       <c r="T36" t="n">
         <v>76.75</v>
       </c>
       <c r="U36" t="n">
-        <v>113</v>
+        <v>105.96</v>
       </c>
       <c r="V36" t="n">
         <v>84.5896</v>
@@ -9528,17 +9526,17 @@
         </is>
       </c>
       <c r="AP36" t="n">
-        <v>627376038055056</v>
+        <v>627376037917376</v>
       </c>
       <c r="AQ36" t="n">
-        <v>-15837799</v>
+        <v>-10394415</v>
       </c>
       <c r="AR36" t="n">
-        <v>63.02</v>
+        <v>63.1</v>
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:17</t>
+          <t>2026-09-11 18:20:09</t>
         </is>
       </c>
       <c r="AT36" t="n">
@@ -9617,19 +9615,19 @@
       </c>
       <c r="BP36" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="BQ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="BR36" t="n">
-        <v>0</v>
+        <v>0.3162</v>
       </c>
       <c r="BS36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT36" t="n">
         <v>0</v>
@@ -9638,29 +9636,29 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>OCDI</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EGX70</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>OCDI</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>EGX70</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E37" t="n">
         <v>32.69</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6513</v>
+        <v>0.6383</v>
       </c>
       <c r="G37" t="n">
         <v>0.3061</v>
@@ -9674,7 +9672,7 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>27.4491</v>
+        <v>27.122</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -9685,10 +9683,10 @@
         <v>13.95</v>
       </c>
       <c r="M37" t="n">
-        <v>2.3814</v>
+        <v>2.3441</v>
       </c>
       <c r="N37" t="n">
-        <v>2323086</v>
+        <v>2325913</v>
       </c>
       <c r="O37" t="n">
         <v>1131777</v>
@@ -9697,13 +9695,13 @@
         <v>0.487</v>
       </c>
       <c r="Q37" t="n">
-        <v>1872029</v>
+        <v>1864069</v>
       </c>
       <c r="R37" t="n">
-        <v>30361</v>
+        <v>178148</v>
       </c>
       <c r="S37" t="n">
-        <v>0.016</v>
+        <v>0.096</v>
       </c>
       <c r="T37" t="n">
         <v>30.03</v>
@@ -9784,17 +9782,17 @@
         </is>
       </c>
       <c r="AP37" t="n">
-        <v>-35181647</v>
+        <v>-35957127</v>
       </c>
       <c r="AQ37" t="n">
-        <v>909732</v>
+        <v>-5653455</v>
       </c>
       <c r="AR37" t="n">
-        <v>62.79</v>
+        <v>62.74</v>
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:17</t>
+          <t>2026-09-11 18:20:09</t>
         </is>
       </c>
       <c r="AT37" t="n">
@@ -9842,16 +9840,16 @@
       </c>
       <c r="BG37" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Avoid</t>
         </is>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 37.4% above EMA200, MACD below signal (bearish), RSI in healthy bullish zone (53.6), accumulation (ADL rising over last 20d); score=46.3/100; entry: enhanced entry at Bollinger Lower Band (overbought (RSI: 53.6)), +0.35% buffer</t>
+          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 37.4% above EMA200, MACD below signal (bearish), RSI in healthy bullish zone (53.6), distribution (ADL falling over last 20d); score=37.7/100; entry: enhanced entry at Bollinger Lower Band (overbought (RSI: 53.6)), +0.35% buffer</t>
         </is>
       </c>
       <c r="BI37" t="n">
-        <v>46.31</v>
+        <v>37.67</v>
       </c>
       <c r="BJ37" t="n">
         <v>10.09</v>
@@ -9866,7 +9864,7 @@
         <v>0</v>
       </c>
       <c r="BN37" t="n">
-        <v>8.65</v>
+        <v>0</v>
       </c>
       <c r="BO37" t="n">
         <v>0</v>
@@ -9894,29 +9892,29 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SVCE</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EGX70</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>SVCE</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>EGX70</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E38" t="n">
         <v>12.33</v>
       </c>
       <c r="F38" t="n">
-        <v>0.244</v>
+        <v>0.2408</v>
       </c>
       <c r="G38" t="n">
         <v>0.0329</v>
@@ -9930,7 +9928,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>19.9529</v>
+        <v>19.8199</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -9941,25 +9939,25 @@
         <v>7.38</v>
       </c>
       <c r="M38" t="n">
-        <v>1.6858</v>
+        <v>1.6709</v>
       </c>
       <c r="N38" t="n">
-        <v>7879435</v>
+        <v>7913453</v>
       </c>
       <c r="O38" t="n">
         <v>14172311</v>
       </c>
       <c r="P38" t="n">
-        <v>1.799</v>
+        <v>1.791</v>
       </c>
       <c r="Q38" t="n">
-        <v>5025011</v>
+        <v>5057015</v>
       </c>
       <c r="R38" t="n">
-        <v>3205044</v>
+        <v>2254678</v>
       </c>
       <c r="S38" t="n">
-        <v>0.638</v>
+        <v>0.446</v>
       </c>
       <c r="T38" t="n">
         <v>10.51</v>
@@ -10040,17 +10038,17 @@
         </is>
       </c>
       <c r="AP38" t="n">
-        <v>-535942562</v>
+        <v>-545605517</v>
       </c>
       <c r="AQ38" t="n">
-        <v>-27550148</v>
+        <v>1595938</v>
       </c>
       <c r="AR38" t="n">
-        <v>68.95</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="AS38" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:17</t>
+          <t>2026-09-11 18:20:09</t>
         </is>
       </c>
       <c r="AT38" t="n">
@@ -10103,11 +10101,11 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 47.9% above EMA200, MACD bullish (strength 10%), MACD above zero (confirmed momentum), RSI in healthy bullish zone (62.5), volume 1.80x average, distribution (ADL falling over last 20d); score=51.9/100; entry: enhanced entry at VWMA (overbought (RSI: 62.5)), +0.35% buffer</t>
+          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 47.9% above EMA200, MACD bullish (strength 10%), MACD above zero (confirmed momentum), RSI in healthy bullish zone (62.5), volume 1.79x average, accumulation (ADL rising over last 20d); score=60.4/100; entry: enhanced entry at VWMA (overbought (RSI: 62.5)), +0.35% buffer</t>
         </is>
       </c>
       <c r="BI38" t="n">
-        <v>51.89</v>
+        <v>60.44</v>
       </c>
       <c r="BJ38" t="n">
         <v>10.09</v>
@@ -10119,10 +10117,10 @@
         <v>27.58</v>
       </c>
       <c r="BM38" t="n">
-        <v>8.369999999999999</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="BN38" t="n">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="BO38" t="n">
         <v>0</v>
@@ -10150,29 +10148,29 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>MOED</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EGX70</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>MOED</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>EGX70</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E39" t="n">
         <v>0.793</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0158</v>
+        <v>0.0155</v>
       </c>
       <c r="G39" t="n">
         <v>0.0036</v>
@@ -10182,11 +10180,11 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>0.7913</v>
+        <v>0.7947</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -10196,22 +10194,22 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="n">
-        <v>36482131</v>
+        <v>36409179</v>
       </c>
       <c r="O39" t="n">
         <v>39563599</v>
       </c>
       <c r="P39" t="n">
-        <v>1.084</v>
+        <v>1.087</v>
       </c>
       <c r="Q39" t="n">
-        <v>40904810</v>
+        <v>40355588</v>
       </c>
       <c r="R39" t="n">
-        <v>17807813</v>
+        <v>16955780</v>
       </c>
       <c r="S39" t="n">
-        <v>0.435</v>
+        <v>0.42</v>
       </c>
       <c r="T39" t="n">
         <v>0.65</v>
@@ -10292,17 +10290,17 @@
         </is>
       </c>
       <c r="AP39" t="n">
-        <v>4698392447857</v>
+        <v>4698386795818</v>
       </c>
       <c r="AQ39" t="n">
-        <v>-24767639</v>
+        <v>53555448</v>
       </c>
       <c r="AR39" t="n">
-        <v>67.34999999999999</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="AS39" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:17</t>
+          <t>2026-09-11 18:20:09</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -10333,11 +10331,11 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 7.8% above EMA200, MACD below signal (bearish), RSI in healthy bullish zone (53.2), distribution (ADL falling over last 20d), Death Cross (SMA50&lt;SMA200) overrides score to Avoid; score=36.2/100; entry: no entry in bearish/unknown regime</t>
+          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 7.8% above EMA200, MACD below signal (bearish), RSI in healthy bullish zone (53.2), accumulation (ADL rising over last 20d), Death Cross (SMA50&lt;SMA200) overrides score to Avoid; score=44.9/100; entry: no entry in bearish/unknown regime</t>
         </is>
       </c>
       <c r="BI39" t="n">
-        <v>36.21</v>
+        <v>44.87</v>
       </c>
       <c r="BJ39" t="n">
         <v>8.359999999999999</v>
@@ -10349,29 +10347,29 @@
         <v>27.58</v>
       </c>
       <c r="BM39" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="BN39" t="n">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="BO39" t="n">
         <v>0</v>
       </c>
       <c r="BP39" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="BQ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid</t>
         </is>
       </c>
       <c r="BR39" t="n">
-        <v>0.3514</v>
+        <v>0.3749</v>
       </c>
       <c r="BS39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT39" t="n">
         <v>1</v>
@@ -10380,29 +10378,29 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>RREI</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>UNINDEX</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>RREI</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>UNINDEX</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E40" t="n">
         <v>4.31</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0835</v>
+        <v>0.0842</v>
       </c>
       <c r="G40" t="n">
         <v>0.0158</v>
@@ -10424,7 +10422,7 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="n">
-        <v>6464302</v>
+        <v>6456515</v>
       </c>
       <c r="O40" t="n">
         <v>1475303</v>
@@ -10433,13 +10431,13 @@
         <v>0.228</v>
       </c>
       <c r="Q40" t="n">
-        <v>4474797</v>
+        <v>4426667</v>
       </c>
       <c r="R40" t="n">
-        <v>162982</v>
+        <v>983535</v>
       </c>
       <c r="S40" t="n">
-        <v>0.036</v>
+        <v>0.222</v>
       </c>
       <c r="T40" t="n">
         <v>4.24</v>
@@ -10520,17 +10518,17 @@
         </is>
       </c>
       <c r="AP40" t="n">
-        <v>784682474589</v>
+        <v>784682966356</v>
       </c>
       <c r="AQ40" t="n">
-        <v>-46941753</v>
+        <v>-47881802</v>
       </c>
       <c r="AR40" t="n">
-        <v>64.33</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="AS40" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:24</t>
+          <t>2026-09-11 18:20:19</t>
         </is>
       </c>
       <c r="AT40" t="n">
@@ -10609,19 +10607,19 @@
       </c>
       <c r="BP40" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="BQ40" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="BR40" t="n">
-        <v>0.3192</v>
+        <v>0</v>
       </c>
       <c r="BS40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT40" t="n">
         <v>0</v>
@@ -10630,29 +10628,29 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ADIB</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EGX30</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>ADIB</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>EGX30</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E41" t="n">
         <v>52.49</v>
       </c>
       <c r="F41" t="n">
-        <v>1.0184</v>
+        <v>1.0249</v>
       </c>
       <c r="G41" t="n">
         <v>0.1743</v>
@@ -10666,7 +10664,7 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>127.003</v>
+        <v>128.1198</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -10677,25 +10675,25 @@
         <v>3.88</v>
       </c>
       <c r="M41" t="n">
-        <v>13.3765</v>
+        <v>13.5208</v>
       </c>
       <c r="N41" t="n">
-        <v>2077381</v>
+        <v>2079911</v>
       </c>
       <c r="O41" t="n">
         <v>1075488</v>
       </c>
       <c r="P41" t="n">
-        <v>0.518</v>
+        <v>0.517</v>
       </c>
       <c r="Q41" t="n">
-        <v>1018983</v>
+        <v>1036646</v>
       </c>
       <c r="R41" t="n">
-        <v>1154400</v>
+        <v>1015068</v>
       </c>
       <c r="S41" t="n">
-        <v>1.133</v>
+        <v>0.979</v>
       </c>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="n">
@@ -10774,17 +10772,17 @@
         </is>
       </c>
       <c r="AP41" t="n">
-        <v>4678490954447</v>
+        <v>4678491909095</v>
       </c>
       <c r="AQ41" t="n">
-        <v>-953493</v>
+        <v>-770579</v>
       </c>
       <c r="AR41" t="n">
-        <v>60.83</v>
+        <v>60.88</v>
       </c>
       <c r="AS41" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:24</t>
+          <t>2026-09-11 18:20:19</t>
         </is>
       </c>
       <c r="AT41" t="n">
@@ -10837,11 +10835,11 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 24.5% above EMA200, MACD below signal (bearish), RSI neutral-firm (49.1), distribution (ADL falling over last 20d); score=27.0/100; entry: enhanced entry at Classic S1 (neutral (RSI: 49.1)), +0.35% buffer</t>
+          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 24.5% above EMA200, MACD below signal (bearish), RSI neutral-firm (49.1), distribution (ADL falling over last 20d); score=26.6/100; entry: enhanced entry at Classic S1 (neutral (RSI: 49.1)), +0.35% buffer</t>
         </is>
       </c>
       <c r="BI41" t="n">
-        <v>27.02</v>
+        <v>26.58</v>
       </c>
       <c r="BJ41" t="n">
         <v>10.04</v>
@@ -10853,7 +10851,7 @@
         <v>16.55</v>
       </c>
       <c r="BM41" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="BN41" t="n">
         <v>0</v>
@@ -10863,19 +10861,19 @@
       </c>
       <c r="BP41" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="BQ41" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="BR41" t="n">
-        <v>0.3586</v>
+        <v>0</v>
       </c>
       <c r="BS41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT41" t="n">
         <v>0</v>
@@ -10884,29 +10882,29 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>MFPC</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>EGX70</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>MFPC</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>EGX70</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E42" t="n">
         <v>47.75</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9367</v>
+        <v>0.9324</v>
       </c>
       <c r="G42" t="n">
         <v>0.5067</v>
@@ -10920,7 +10918,7 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>52.9005</v>
+        <v>52.8917</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -10931,25 +10929,25 @@
         <v>9.119999999999999</v>
       </c>
       <c r="M42" t="n">
-        <v>5.234</v>
+        <v>5.2329</v>
       </c>
       <c r="N42" t="n">
-        <v>2101940</v>
+        <v>2106745</v>
       </c>
       <c r="O42" t="n">
         <v>1450237</v>
       </c>
       <c r="P42" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="Q42" t="n">
-        <v>1377292</v>
+        <v>1392527</v>
       </c>
       <c r="R42" t="n">
-        <v>2446714</v>
+        <v>966825</v>
       </c>
       <c r="S42" t="n">
-        <v>1.776</v>
+        <v>0.694</v>
       </c>
       <c r="T42" t="n">
         <v>35.37</v>
@@ -11028,17 +11026,17 @@
         </is>
       </c>
       <c r="AP42" t="n">
-        <v>11377379377095</v>
+        <v>11377379707483</v>
       </c>
       <c r="AQ42" t="n">
-        <v>13465798</v>
+        <v>16871502</v>
       </c>
       <c r="AR42" t="n">
-        <v>62.12</v>
+        <v>62.16</v>
       </c>
       <c r="AS42" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:24</t>
+          <t>2026-09-11 18:20:19</t>
         </is>
       </c>
       <c r="AT42" t="n">
@@ -11059,11 +11057,11 @@
         <v>49.6333</v>
       </c>
       <c r="AY42" t="n">
-        <v>52.9194</v>
+        <v>53.0583</v>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 49.3; TP2: Classic R3 at 49.63; TP3: ATR target (full) at 52.92</t>
+          <t>TP1: Bollinger Upper Band at 49.3; TP2: Classic R3 at 49.63; TP3: ATR target (full) at 53.06</t>
         </is>
       </c>
       <c r="BA42" t="n">
@@ -11073,7 +11071,7 @@
         <v>27.98</v>
       </c>
       <c r="BC42" t="n">
-        <v>48.89</v>
+        <v>49.78</v>
       </c>
       <c r="BD42" t="n">
         <v>8.98</v>
@@ -11082,20 +11080,20 @@
         <v>9.720000000000001</v>
       </c>
       <c r="BF42" t="n">
-        <v>16.99</v>
+        <v>17.29</v>
       </c>
       <c r="BG42" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Avoid</t>
         </is>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 26.3% above EMA200, MACD bullish (strength 34%), MACD above zero (confirmed momentum), RSI overbought (78.2) (strong trend, penalty reduced), buy-volume spike (1.78x), accumulation (ADL rising over last 20d); score=43.1/100; entry: enhanced entry at Parabolic SAR (overbought (RSI: 78.2)), +0.35% buffer</t>
+          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 26.3% above EMA200, MACD bullish (strength 34%), MACD above zero (confirmed momentum), RSI overbought (78.2) (strong trend, penalty reduced), accumulation (ADL rising over last 20d); score=35.7/100; entry: enhanced entry at Parabolic SAR (overbought (RSI: 78.2)), +0.35% buffer</t>
         </is>
       </c>
       <c r="BI42" t="n">
-        <v>43.11</v>
+        <v>35.74</v>
       </c>
       <c r="BJ42" t="n">
         <v>10.09</v>
@@ -11107,7 +11105,7 @@
         <v>9.65</v>
       </c>
       <c r="BM42" t="n">
-        <v>7.36</v>
+        <v>0</v>
       </c>
       <c r="BN42" t="n">
         <v>8.65</v>
@@ -11117,19 +11115,19 @@
       </c>
       <c r="BP42" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="BQ42" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="BR42" t="n">
-        <v>0.4429</v>
+        <v>0.4566</v>
       </c>
       <c r="BS42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT42" t="n">
         <v>1</v>
@@ -11138,29 +11136,29 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>NCCW</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>EGX70</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>NCCW</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>EGX70</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E43" t="n">
         <v>7.6</v>
       </c>
       <c r="F43" t="n">
-        <v>0.1398</v>
+        <v>0.1484</v>
       </c>
       <c r="G43" t="n">
         <v>0.0241</v>
@@ -11170,34 +11168,36 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>8.118399999999999</v>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>USD-Comparison (fallback)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="n">
-        <v>2989567</v>
+        <v>3056074</v>
       </c>
       <c r="O43" t="n">
         <v>20941631</v>
       </c>
       <c r="P43" t="n">
-        <v>7.005</v>
+        <v>6.852</v>
       </c>
       <c r="Q43" t="n">
-        <v>2735713</v>
+        <v>3011587</v>
       </c>
       <c r="R43" t="n">
-        <v>25341698</v>
+        <v>16182163</v>
       </c>
       <c r="S43" t="n">
-        <v>9.263</v>
+        <v>5.373</v>
       </c>
       <c r="T43" t="n">
         <v>5.77</v>
@@ -11276,17 +11276,17 @@
         </is>
       </c>
       <c r="AP43" t="n">
-        <v>16328582020100</v>
+        <v>16328594264486</v>
       </c>
       <c r="AQ43" t="n">
-        <v>3585671</v>
+        <v>12693785</v>
       </c>
       <c r="AR43" t="n">
-        <v>64.01000000000001</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="AS43" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:24</t>
+          <t>2026-09-11 18:20:19</t>
         </is>
       </c>
       <c r="AT43" t="n">
@@ -11307,11 +11307,11 @@
         <v>9.23</v>
       </c>
       <c r="AY43" t="n">
-        <v>8.3933</v>
+        <v>8.621</v>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 7.71; TP2: Classic R3 at 9.23; TP3: ATR target (full) at 8.39</t>
+          <t>TP1: Classic R2 at 7.71; TP2: Classic R3 at 9.23; TP3: ATR target (full) at 8.62</t>
         </is>
       </c>
       <c r="BA43" t="n">
@@ -11321,7 +11321,7 @@
         <v>2.67</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.78</v>
+        <v>2.02</v>
       </c>
       <c r="BD43" t="n">
         <v>14.76</v>
@@ -11330,7 +11330,7 @@
         <v>37.39</v>
       </c>
       <c r="BF43" t="n">
-        <v>24.93</v>
+        <v>28.32</v>
       </c>
       <c r="BG43" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 49.8% above EMA200, MACD bullish (strength 80%), MACD above zero (confirmed momentum), RSI overbought (79.4) (strong trend, penalty reduced), volume 7.00x average, buy-volume spike (9.26x), accumulation (ADL rising over last 20d); score=56.5/100; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 79.4)), +0.35% buffer</t>
+          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 49.8% above EMA200, MACD bullish (strength 80%), MACD above zero (confirmed momentum), RSI overbought (79.4) (strong trend, penalty reduced), volume 6.85x average, buy-volume spike (5.37x), accumulation (ADL rising over last 20d); score=56.5/100; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 79.4)), +0.35% buffer</t>
         </is>
       </c>
       <c r="BI43" t="n">
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="BR43" t="n">
-        <v>0.3243</v>
+        <v>0.3685</v>
       </c>
       <c r="BS43" t="n">
         <v>0</v>
@@ -11386,29 +11386,29 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>EALR</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>UNINDEX</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>EALR</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>UNINDEX</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E44" t="n">
         <v>375.62</v>
       </c>
       <c r="F44" t="n">
-        <v>7.3364</v>
+        <v>7.3345</v>
       </c>
       <c r="G44" t="n">
         <v>0.2706</v>
@@ -11422,7 +11422,7 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>380.8715</v>
+        <v>381.1103</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -11436,22 +11436,22 @@
         <v>0.7903</v>
       </c>
       <c r="N44" t="n">
-        <v>38934</v>
+        <v>38847</v>
       </c>
       <c r="O44" t="n">
         <v>12283</v>
       </c>
       <c r="P44" t="n">
-        <v>0.315</v>
+        <v>0.316</v>
       </c>
       <c r="Q44" t="n">
-        <v>24884</v>
+        <v>24256</v>
       </c>
       <c r="R44" t="n">
-        <v>1546</v>
+        <v>4456</v>
       </c>
       <c r="S44" t="n">
-        <v>0.062</v>
+        <v>0.184</v>
       </c>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="n">
@@ -11530,17 +11530,17 @@
         </is>
       </c>
       <c r="AP44" t="n">
-        <v>5135111409851936</v>
+        <v>5135111409848566</v>
       </c>
       <c r="AQ44" t="n">
-        <v>-140154</v>
+        <v>-102490</v>
       </c>
       <c r="AR44" t="n">
-        <v>69.37</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="AS44" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:24</t>
+          <t>2026-09-11 18:20:19</t>
         </is>
       </c>
       <c r="AT44" t="n">
@@ -11619,50 +11619,50 @@
       </c>
       <c r="BP44" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="BQ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid</t>
         </is>
       </c>
       <c r="BR44" t="n">
         <v>0.4361</v>
       </c>
       <c r="BS44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>AALR</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>UNINDEX</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>AALR</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>UNINDEX</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E45" t="n">
         <v>306.85</v>
       </c>
       <c r="F45" t="n">
-        <v>5.9459</v>
+        <v>5.9917</v>
       </c>
       <c r="G45" t="n">
         <v>0.4772</v>
@@ -11672,36 +11672,40 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>308.8033</v>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>USD-Comparison (fallback)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="n">
-        <v>84378</v>
+        <v>83921</v>
       </c>
       <c r="O45" t="n">
         <v>32352</v>
       </c>
       <c r="P45" t="n">
-        <v>0.383</v>
+        <v>0.386</v>
       </c>
       <c r="Q45" t="n">
-        <v>51080</v>
+        <v>49701</v>
       </c>
       <c r="R45" t="n">
-        <v>2794</v>
+        <v>16699</v>
       </c>
       <c r="S45" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="T45" t="inlineStr"/>
+        <v>0.336</v>
+      </c>
+      <c r="T45" t="n">
+        <v>295</v>
+      </c>
       <c r="U45" t="n">
         <v>317.99</v>
       </c>
@@ -11778,17 +11782,17 @@
         </is>
       </c>
       <c r="AP45" t="n">
-        <v>349550286280193</v>
+        <v>349550286281240</v>
       </c>
       <c r="AQ45" t="n">
-        <v>-616650</v>
+        <v>-574915</v>
       </c>
       <c r="AR45" t="n">
-        <v>71.7</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:24</t>
+          <t>2026-09-11 18:20:19</t>
         </is>
       </c>
       <c r="AT45" t="n">
@@ -11867,19 +11871,19 @@
       </c>
       <c r="BP45" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="BQ45" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="BR45" t="n">
-        <v>0.3494</v>
+        <v>0</v>
       </c>
       <c r="BS45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT45" t="n">
         <v>0</v>
@@ -11888,29 +11892,29 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>KABO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>EGX70</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>KABO</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>EGX70</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E46" t="n">
         <v>9.5</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1863</v>
+        <v>0.1855</v>
       </c>
       <c r="G46" t="n">
         <v>0.0239</v>
@@ -11932,22 +11936,22 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="n">
-        <v>2751460</v>
+        <v>2762231</v>
       </c>
       <c r="O46" t="n">
         <v>3934103</v>
       </c>
       <c r="P46" t="n">
-        <v>1.43</v>
+        <v>1.424</v>
       </c>
       <c r="Q46" t="n">
-        <v>2364474</v>
+        <v>2289452</v>
       </c>
       <c r="R46" t="n">
-        <v>3605844</v>
+        <v>1311372</v>
       </c>
       <c r="S46" t="n">
-        <v>1.525</v>
+        <v>0.573</v>
       </c>
       <c r="T46" t="n">
         <v>7.75</v>
@@ -12028,17 +12032,17 @@
         </is>
       </c>
       <c r="AP46" t="n">
-        <v>1000000012315</v>
+        <v>999998700956</v>
       </c>
       <c r="AQ46" t="n">
-        <v>-14865664</v>
+        <v>-16367699</v>
       </c>
       <c r="AR46" t="n">
-        <v>66.90000000000001</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="AS46" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:24</t>
+          <t>2026-09-11 18:20:19</t>
         </is>
       </c>
       <c r="AT46" t="n">
@@ -12086,16 +12090,16 @@
       </c>
       <c r="BG46" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Avoid</t>
         </is>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 36.6% above EMA200, MACD below signal (bearish), RSI in healthy bullish zone (65.2), distribution (ADL falling over last 20d); score=40.8/100; entry: enhanced entry at VWMA (overbought (RSI: 65.2)), +0.35% buffer</t>
+          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 36.6% above EMA200, MACD below signal (bearish), RSI in healthy bullish zone (65.2), distribution (ADL falling over last 20d); score=39.1/100; entry: enhanced entry at VWMA (overbought (RSI: 65.2)), +0.35% buffer</t>
         </is>
       </c>
       <c r="BI46" t="n">
-        <v>40.81</v>
+        <v>39.06</v>
       </c>
       <c r="BJ46" t="n">
         <v>10.09</v>
@@ -12107,7 +12111,7 @@
         <v>27.58</v>
       </c>
       <c r="BM46" t="n">
-        <v>3.14</v>
+        <v>1.39</v>
       </c>
       <c r="BN46" t="n">
         <v>0</v>
@@ -12126,7 +12130,7 @@
         </is>
       </c>
       <c r="BR46" t="n">
-        <v>0.5234</v>
+        <v>0.4994</v>
       </c>
       <c r="BS46" t="n">
         <v>0</v>
@@ -12138,29 +12142,29 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>MCRO</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>EGX70</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>MCRO</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>EGX70</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E47" t="n">
         <v>1.68</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0335</v>
+        <v>0.0328</v>
       </c>
       <c r="G47" t="n">
         <v>0.015</v>
@@ -12174,7 +12178,7 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>0.6708</v>
+        <v>0.6619</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -12185,25 +12189,25 @@
         <v>30.08</v>
       </c>
       <c r="M47" t="n">
-        <v>0.0568</v>
+        <v>0.0558</v>
       </c>
       <c r="N47" t="n">
-        <v>46621099</v>
+        <v>46779512</v>
       </c>
       <c r="O47" t="n">
         <v>54495672</v>
       </c>
       <c r="P47" t="n">
-        <v>1.169</v>
+        <v>1.165</v>
       </c>
       <c r="Q47" t="n">
-        <v>41509082</v>
+        <v>39106908</v>
       </c>
       <c r="R47" t="n">
-        <v>49536232</v>
+        <v>7785083</v>
       </c>
       <c r="S47" t="n">
-        <v>1.193</v>
+        <v>0.199</v>
       </c>
       <c r="T47" t="n">
         <v>1.48</v>
@@ -12284,17 +12288,17 @@
         </is>
       </c>
       <c r="AP47" t="n">
-        <v>-1991013134</v>
+        <v>-2029938641</v>
       </c>
       <c r="AQ47" t="n">
-        <v>-23890198</v>
+        <v>-62815838</v>
       </c>
       <c r="AR47" t="n">
-        <v>66.04000000000001</v>
+        <v>65.72</v>
       </c>
       <c r="AS47" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:24</t>
+          <t>2026-09-11 18:20:19</t>
         </is>
       </c>
       <c r="AT47" t="n">
@@ -12347,11 +12351,11 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 34.2% above EMA200, MACD bullish (strength 38%), MACD above zero (confirmed momentum), RSI in healthy bullish zone (65.5), distribution (ADL falling over last 20d); score=46.5/100; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 65.5)), +0.35% buffer</t>
+          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 34.2% above EMA200, MACD bullish (strength 38%), MACD above zero (confirmed momentum), RSI in healthy bullish zone (65.5), distribution (ADL falling over last 20d); score=45.8/100; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 65.5)), +0.35% buffer</t>
         </is>
       </c>
       <c r="BI47" t="n">
-        <v>46.47</v>
+        <v>45.82</v>
       </c>
       <c r="BJ47" t="n">
         <v>10.09</v>
@@ -12363,7 +12367,7 @@
         <v>27.58</v>
       </c>
       <c r="BM47" t="n">
-        <v>1.19</v>
+        <v>0.54</v>
       </c>
       <c r="BN47" t="n">
         <v>0</v>
@@ -12373,19 +12377,19 @@
       </c>
       <c r="BP47" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="BQ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="BR47" t="n">
-        <v>0</v>
+        <v>0.3127</v>
       </c>
       <c r="BS47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT47" t="n">
         <v>0</v>
@@ -12394,29 +12398,29 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>GGCC</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>UNINDEX</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>GGCC</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>UNINDEX</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E48" t="n">
         <v>0.877</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0167</v>
+        <v>0.0171</v>
       </c>
       <c r="G48" t="n">
         <v>0.0066</v>
@@ -12430,7 +12434,7 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>0.8601</v>
+        <v>0.8975</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -12444,25 +12448,25 @@
         <v>0.0543</v>
       </c>
       <c r="N48" t="n">
-        <v>22625301</v>
+        <v>22656040</v>
       </c>
       <c r="O48" t="n">
         <v>17171652</v>
       </c>
       <c r="P48" t="n">
-        <v>0.759</v>
+        <v>0.758</v>
       </c>
       <c r="Q48" t="n">
-        <v>21460949</v>
+        <v>21444703</v>
       </c>
       <c r="R48" t="n">
-        <v>5640230</v>
+        <v>16063785</v>
       </c>
       <c r="S48" t="n">
-        <v>0.263</v>
+        <v>0.749</v>
       </c>
       <c r="T48" t="n">
-        <v>0.805</v>
+        <v>0.83</v>
       </c>
       <c r="U48" t="n">
         <v>1.04</v>
@@ -12540,17 +12544,17 @@
         </is>
       </c>
       <c r="AP48" t="n">
-        <v>-2400076911198</v>
+        <v>-2400061955280</v>
       </c>
       <c r="AQ48" t="n">
-        <v>-426728532</v>
+        <v>-390348905</v>
       </c>
       <c r="AR48" t="n">
-        <v>65.3</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="AS48" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:24</t>
+          <t>2026-09-11 18:20:19</t>
         </is>
       </c>
       <c r="AT48" t="n">
@@ -12638,41 +12642,41 @@
         </is>
       </c>
       <c r="BR48" t="n">
-        <v>0</v>
+        <v>0.3649</v>
       </c>
       <c r="BS48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>INEG</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>UNINDEX</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>INEG</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>UNINDEX</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E49" t="n">
         <v>0.647</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0116</v>
+        <v>0.0126</v>
       </c>
       <c r="G49" t="n">
         <v>0.0031</v>
@@ -12694,29 +12698,27 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="n">
-        <v>21992842</v>
+        <v>21945975</v>
       </c>
       <c r="O49" t="n">
         <v>15796702</v>
       </c>
       <c r="P49" t="n">
-        <v>0.718</v>
+        <v>0.72</v>
       </c>
       <c r="Q49" t="n">
-        <v>22448599</v>
+        <v>21936339</v>
       </c>
       <c r="R49" t="n">
-        <v>29343849</v>
+        <v>7898351</v>
       </c>
       <c r="S49" t="n">
-        <v>1.307</v>
+        <v>0.36</v>
       </c>
       <c r="T49" t="n">
         <v>0.518</v>
       </c>
-      <c r="U49" t="n">
-        <v>0.644</v>
-      </c>
+      <c r="U49" t="inlineStr"/>
       <c r="V49" t="n">
         <v>0.508</v>
       </c>
@@ -12793,14 +12795,14 @@
         <v>193565791577626</v>
       </c>
       <c r="AQ49" t="n">
-        <v>-166517975</v>
+        <v>-132351307</v>
       </c>
       <c r="AR49" t="n">
-        <v>63.5</v>
+        <v>63.59</v>
       </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:24</t>
+          <t>2026-09-11 18:20:19</t>
         </is>
       </c>
       <c r="AT49" t="n">
@@ -12818,33 +12820,33 @@
         <v>0.706</v>
       </c>
       <c r="AX49" t="n">
-        <v>0.6591</v>
+        <v>0.6707</v>
       </c>
       <c r="AY49" t="n">
-        <v>0.7015</v>
+        <v>0.7188</v>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>TP1: Classic R3 at 0.71; TP2: ATR target (2/3) at 0.66; TP3: ATR target (full) at 0.7</t>
+          <t>TP1: Classic R3 at 0.71; TP2: ATR target (2/3) at 0.67; TP3: ATR target (full) at 0.72</t>
         </is>
       </c>
       <c r="BA49" t="n">
         <v>2.97</v>
       </c>
       <c r="BB49" t="n">
-        <v>1.91</v>
+        <v>2.17</v>
       </c>
       <c r="BC49" t="n">
-        <v>2.87</v>
+        <v>3.26</v>
       </c>
       <c r="BD49" t="n">
         <v>22.89</v>
       </c>
       <c r="BE49" t="n">
-        <v>14.73</v>
+        <v>16.75</v>
       </c>
       <c r="BF49" t="n">
-        <v>22.11</v>
+        <v>25.12</v>
       </c>
       <c r="BG49" t="inlineStr">
         <is>
@@ -12853,11 +12855,11 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 39.2% above EMA200, MACD bullish (strength 58%), MACD above zero (confirmed momentum), RSI overbought (76.0) (strong trend, penalty reduced), distribution (ADL falling over last 20d); score=29.6/100; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 76.0)), +0.35% buffer</t>
+          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 39.2% above EMA200, MACD bullish (strength 58%), MACD above zero (confirmed momentum), RSI overbought (76.0) (strong trend, penalty reduced), distribution (ADL falling over last 20d); score=28.6/100; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 76.0)), +0.35% buffer</t>
         </is>
       </c>
       <c r="BI49" t="n">
-        <v>29.61</v>
+        <v>28.6</v>
       </c>
       <c r="BJ49" t="n">
         <v>10.09</v>
@@ -12869,7 +12871,7 @@
         <v>9.65</v>
       </c>
       <c r="BM49" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN49" t="n">
         <v>0</v>
@@ -12888,41 +12890,41 @@
         </is>
       </c>
       <c r="BR49" t="n">
-        <v>0.4208</v>
+        <v>0.347</v>
       </c>
       <c r="BS49" t="n">
         <v>0</v>
       </c>
       <c r="BT49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CPCI</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>UNINDEX</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>CPCI</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>UNINDEX</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E50" t="n">
         <v>539.9</v>
       </c>
       <c r="F50" t="n">
-        <v>10.5623</v>
+        <v>10.4722</v>
       </c>
       <c r="G50" t="n">
         <v>0.3324</v>
@@ -12936,7 +12938,7 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>546.5626999999999</v>
+        <v>547.4509</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -12946,22 +12948,22 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="n">
-        <v>12580</v>
+        <v>12428</v>
       </c>
       <c r="O50" t="n">
         <v>2593</v>
       </c>
       <c r="P50" t="n">
-        <v>0.206</v>
+        <v>0.209</v>
       </c>
       <c r="Q50" t="n">
-        <v>7409</v>
+        <v>7402</v>
       </c>
       <c r="R50" t="n">
-        <v>438</v>
+        <v>614</v>
       </c>
       <c r="S50" t="n">
-        <v>0.059</v>
+        <v>0.083</v>
       </c>
       <c r="T50" t="n">
         <v>440.01</v>
@@ -13042,17 +13044,17 @@
         </is>
       </c>
       <c r="AP50" t="n">
-        <v>37433669428870</v>
+        <v>37433667729869</v>
       </c>
       <c r="AQ50" t="n">
-        <v>-90772</v>
+        <v>-79231</v>
       </c>
       <c r="AR50" t="n">
-        <v>68.04000000000001</v>
+        <v>67.97</v>
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:24</t>
+          <t>2026-09-11 18:20:19</t>
         </is>
       </c>
       <c r="AT50" t="n">
@@ -13152,29 +13154,29 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>AXPH</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>UNINDEX</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>AXPH</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>UNINDEX</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E51" t="n">
         <v>1688</v>
       </c>
       <c r="F51" t="n">
-        <v>32.6233</v>
+        <v>32.7764</v>
       </c>
       <c r="G51" t="n">
         <v>1.2095</v>
@@ -13196,22 +13198,22 @@
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="n">
-        <v>2921</v>
+        <v>2907</v>
       </c>
       <c r="O51" t="n">
         <v>3415</v>
       </c>
       <c r="P51" t="n">
-        <v>1.169</v>
+        <v>1.175</v>
       </c>
       <c r="Q51" t="n">
-        <v>2066</v>
+        <v>2094</v>
       </c>
       <c r="R51" t="n">
-        <v>270</v>
+        <v>1539</v>
       </c>
       <c r="S51" t="n">
-        <v>0.131</v>
+        <v>0.735</v>
       </c>
       <c r="T51" t="n">
         <v>1121.5601</v>
@@ -13292,17 +13294,17 @@
         </is>
       </c>
       <c r="AP51" t="n">
-        <v>704433105603352</v>
+        <v>704433059945748</v>
       </c>
       <c r="AQ51" t="n">
-        <v>-23050</v>
+        <v>-24080</v>
       </c>
       <c r="AR51" t="n">
-        <v>66.3</v>
+        <v>66.45</v>
       </c>
       <c r="AS51" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:24</t>
+          <t>2026-09-11 18:20:19</t>
         </is>
       </c>
       <c r="AT51" t="n">
@@ -13359,7 +13361,7 @@
         </is>
       </c>
       <c r="BI51" t="n">
-        <v>20.3</v>
+        <v>20.32</v>
       </c>
       <c r="BJ51" t="n">
         <v>10.09</v>
@@ -13371,7 +13373,7 @@
         <v>9.65</v>
       </c>
       <c r="BM51" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BN51" t="n">
         <v>0</v>
@@ -13402,29 +13404,29 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>MBSC</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>UNINDEX</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>MBSC</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>UNINDEX</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E52" t="n">
         <v>417.98</v>
       </c>
       <c r="F52" t="n">
-        <v>8.330500000000001</v>
+        <v>8.1616</v>
       </c>
       <c r="G52" t="n">
         <v>0.4037</v>
@@ -13438,7 +13440,7 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>796.8049</v>
+        <v>774.8624</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -13446,28 +13448,28 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>4.42</v>
+        <v>4.5</v>
       </c>
       <c r="M52" t="n">
-        <v>96.0061</v>
+        <v>92.94110000000001</v>
       </c>
       <c r="N52" t="n">
-        <v>112088</v>
+        <v>112229</v>
       </c>
       <c r="O52" t="n">
         <v>39744</v>
       </c>
       <c r="P52" t="n">
-        <v>0.355</v>
+        <v>0.354</v>
       </c>
       <c r="Q52" t="n">
-        <v>101826</v>
+        <v>101835</v>
       </c>
       <c r="R52" t="n">
-        <v>424171</v>
+        <v>19726</v>
       </c>
       <c r="S52" t="n">
-        <v>4.166</v>
+        <v>0.194</v>
       </c>
       <c r="T52" t="n">
         <v>240.02</v>
@@ -13548,17 +13550,17 @@
         </is>
       </c>
       <c r="AP52" t="n">
-        <v>56932920039709</v>
+        <v>56932924313514</v>
       </c>
       <c r="AQ52" t="n">
-        <v>410064</v>
+        <v>354089</v>
       </c>
       <c r="AR52" t="n">
-        <v>56.57</v>
+        <v>56.47</v>
       </c>
       <c r="AS52" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:24</t>
+          <t>2026-09-11 18:20:19</t>
         </is>
       </c>
       <c r="AT52" t="n">
@@ -13606,16 +13608,16 @@
       </c>
       <c r="BG52" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 56.4% above EMA200, MACD below signal (bearish), RSI in healthy bullish zone (60.8), buy-volume spike (4.17x), accumulation (ADL rising over last 20d); score=65.9/100; entry: enhanced entry at VWMA (overbought (RSI: 60.8)), +0.35% buffer</t>
+          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 56.4% above EMA200, MACD below signal (bearish), RSI in healthy bullish zone (60.8), accumulation (ADL rising over last 20d); score=48.0/100; entry: enhanced entry at VWMA (overbought (RSI: 60.8)), +0.35% buffer</t>
         </is>
       </c>
       <c r="BI52" t="n">
-        <v>65.94</v>
+        <v>48.04</v>
       </c>
       <c r="BJ52" t="n">
         <v>10.09</v>
@@ -13627,7 +13629,7 @@
         <v>27.58</v>
       </c>
       <c r="BM52" t="n">
-        <v>17.9</v>
+        <v>0</v>
       </c>
       <c r="BN52" t="n">
         <v>10.38</v>
@@ -13637,50 +13639,50 @@
       </c>
       <c r="BP52" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="BQ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid</t>
         </is>
       </c>
       <c r="BR52" t="n">
-        <v>0</v>
+        <v>0.3213</v>
       </c>
       <c r="BS52" t="n">
         <v>0</v>
       </c>
       <c r="BT52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>MILS</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>UNINDEX</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>MILS</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>UNINDEX</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E53" t="n">
         <v>201.51</v>
       </c>
       <c r="F53" t="n">
-        <v>3.9816</v>
+        <v>3.9348</v>
       </c>
       <c r="G53" t="n">
         <v>0.4597</v>
@@ -13702,22 +13704,22 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="n">
-        <v>114047</v>
+        <v>114152</v>
       </c>
       <c r="O53" t="n">
         <v>27337</v>
       </c>
       <c r="P53" t="n">
-        <v>0.24</v>
+        <v>0.239</v>
       </c>
       <c r="Q53" t="n">
-        <v>153469</v>
+        <v>151645</v>
       </c>
       <c r="R53" t="n">
-        <v>11116</v>
+        <v>110</v>
       </c>
       <c r="S53" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.001</v>
       </c>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="n">
@@ -13796,17 +13798,17 @@
         </is>
       </c>
       <c r="AP53" t="n">
-        <v>107581384576368</v>
+        <v>107581379164492</v>
       </c>
       <c r="AQ53" t="n">
-        <v>-800714</v>
+        <v>-569283</v>
       </c>
       <c r="AR53" t="n">
-        <v>68.70999999999999</v>
+        <v>68.64</v>
       </c>
       <c r="AS53" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:24</t>
+          <t>2026-09-11 18:20:19</t>
         </is>
       </c>
       <c r="AT53" t="n">
@@ -13885,19 +13887,19 @@
       </c>
       <c r="BP53" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="BQ53" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="BR53" t="n">
-        <v>0.5191</v>
+        <v>0</v>
       </c>
       <c r="BS53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT53" t="n">
         <v>0</v>
@@ -13906,29 +13908,29 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ZMID</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>EGX70</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>ZMID</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>EGX70</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E54" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="F54" t="n">
-        <v>0.1883</v>
+        <v>0.1914</v>
       </c>
       <c r="G54" t="n">
         <v>0.0563</v>
@@ -13942,7 +13944,7 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>8.870900000000001</v>
+        <v>9.017899999999999</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -13953,10 +13955,10 @@
         <v>10.94</v>
       </c>
       <c r="M54" t="n">
-        <v>0.8774</v>
+        <v>0.8956</v>
       </c>
       <c r="N54" t="n">
-        <v>25905892</v>
+        <v>25887985</v>
       </c>
       <c r="O54" t="n">
         <v>12115198</v>
@@ -13965,13 +13967,13 @@
         <v>0.468</v>
       </c>
       <c r="Q54" t="n">
-        <v>16120928</v>
+        <v>15394951</v>
       </c>
       <c r="R54" t="n">
-        <v>11839737</v>
+        <v>12115198</v>
       </c>
       <c r="S54" t="n">
-        <v>0.734</v>
+        <v>0.787</v>
       </c>
       <c r="T54" t="n">
         <v>7.39</v>
@@ -14050,17 +14052,17 @@
         </is>
       </c>
       <c r="AP54" t="n">
-        <v>303724411341871</v>
+        <v>303724404780082</v>
       </c>
       <c r="AQ54" t="n">
-        <v>136383103</v>
+        <v>142151866</v>
       </c>
       <c r="AR54" t="n">
-        <v>65.78</v>
+        <v>65.83</v>
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:24</t>
+          <t>2026-09-11 18:20:19</t>
         </is>
       </c>
       <c r="AT54" t="n">
@@ -14160,29 +14162,29 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>AMIA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>EGX70</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>AMIA</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>EGX70</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E55" t="n">
         <v>19.17</v>
       </c>
       <c r="F55" t="n">
-        <v>0.3671</v>
+        <v>0.3743</v>
       </c>
       <c r="G55" t="n">
         <v>0.024</v>
@@ -14208,22 +14210,22 @@
         <v>0.8196</v>
       </c>
       <c r="N55" t="n">
-        <v>3326014</v>
+        <v>3290875</v>
       </c>
       <c r="O55" t="n">
         <v>242486</v>
       </c>
       <c r="P55" t="n">
-        <v>0.073</v>
+        <v>0.074</v>
       </c>
       <c r="Q55" t="n">
-        <v>1489819</v>
+        <v>1489351</v>
       </c>
       <c r="R55" t="n">
-        <v>16068</v>
+        <v>242486</v>
       </c>
       <c r="S55" t="n">
-        <v>0.011</v>
+        <v>0.163</v>
       </c>
       <c r="T55" t="n">
         <v>18.5</v>
@@ -14304,17 +14306,17 @@
         </is>
       </c>
       <c r="AP55" t="n">
-        <v>715005415351</v>
+        <v>715005636163</v>
       </c>
       <c r="AQ55" t="n">
-        <v>3883684</v>
+        <v>3379016</v>
       </c>
       <c r="AR55" t="n">
-        <v>66.19</v>
+        <v>66.23</v>
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:24</t>
+          <t>2026-09-11 18:20:19</t>
         </is>
       </c>
       <c r="AT55" t="n">
@@ -14414,29 +14416,29 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>MISR</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>UNINDEX</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>MISR</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>UNINDEX</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E56" t="n">
         <v>5.51</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1081</v>
+        <v>0.1076</v>
       </c>
       <c r="G56" t="n">
         <v>0.1008</v>
@@ -14450,7 +14452,7 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>5.6371</v>
+        <v>5.6612</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -14560,7 +14562,7 @@
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:24</t>
+          <t>2026-09-11 18:20:19</t>
         </is>
       </c>
       <c r="AT56" t="n">
@@ -14660,29 +14662,29 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>MPCI</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>EGX70</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>MPCI</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>EGX70</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E57" t="n">
         <v>421.99</v>
       </c>
       <c r="F57" t="n">
-        <v>8.3346</v>
+        <v>8.2399</v>
       </c>
       <c r="G57" t="n">
         <v>0.3911</v>
@@ -14708,7 +14710,7 @@
         <v>22.7816</v>
       </c>
       <c r="N57" t="n">
-        <v>378530</v>
+        <v>377452</v>
       </c>
       <c r="O57" t="n">
         <v>94873</v>
@@ -14717,13 +14719,13 @@
         <v>0.251</v>
       </c>
       <c r="Q57" t="n">
-        <v>195236</v>
+        <v>196372</v>
       </c>
       <c r="R57" t="n">
-        <v>95854</v>
+        <v>64813</v>
       </c>
       <c r="S57" t="n">
-        <v>0.491</v>
+        <v>0.33</v>
       </c>
       <c r="T57" t="n">
         <v>345</v>
@@ -14804,17 +14806,17 @@
         </is>
       </c>
       <c r="AP57" t="n">
-        <v>142484484822355</v>
+        <v>142484483774628</v>
       </c>
       <c r="AQ57" t="n">
-        <v>-928986</v>
+        <v>-849288</v>
       </c>
       <c r="AR57" t="n">
-        <v>62.72</v>
+        <v>62.61</v>
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:24</t>
+          <t>2026-09-11 18:20:19</t>
         </is>
       </c>
       <c r="AT57" t="n">
@@ -14914,29 +14916,29 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>TALM</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>EGX70</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>TALM</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>EGX70</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E58" t="n">
         <v>18</v>
       </c>
       <c r="F58" t="n">
-        <v>0.355</v>
+        <v>0.3515</v>
       </c>
       <c r="G58" t="n">
         <v>0.1004</v>
@@ -14950,7 +14952,7 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>16.6402</v>
+        <v>16.5631</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -14961,25 +14963,25 @@
         <v>9.640000000000001</v>
       </c>
       <c r="M58" t="n">
-        <v>1.8779</v>
+        <v>1.8675</v>
       </c>
       <c r="N58" t="n">
-        <v>802307</v>
+        <v>806138</v>
       </c>
       <c r="O58" t="n">
         <v>1011018</v>
       </c>
       <c r="P58" t="n">
-        <v>1.26</v>
+        <v>1.254</v>
       </c>
       <c r="Q58" t="n">
-        <v>755449</v>
+        <v>754838</v>
       </c>
       <c r="R58" t="n">
-        <v>218136</v>
+        <v>129616</v>
       </c>
       <c r="S58" t="n">
-        <v>0.289</v>
+        <v>0.172</v>
       </c>
       <c r="T58" t="n">
         <v>17.11</v>
@@ -15060,17 +15062,17 @@
         </is>
       </c>
       <c r="AP58" t="n">
-        <v>10706269906338</v>
+        <v>10706269154551</v>
       </c>
       <c r="AQ58" t="n">
-        <v>-4229866</v>
+        <v>-3884243</v>
       </c>
       <c r="AR58" t="n">
-        <v>71.01000000000001</v>
+        <v>70.87</v>
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:24</t>
+          <t>2026-09-11 18:20:19</t>
         </is>
       </c>
       <c r="AT58" t="n">
@@ -15127,7 +15129,7 @@
         </is>
       </c>
       <c r="BI58" t="n">
-        <v>26.31</v>
+        <v>26.29</v>
       </c>
       <c r="BJ58" t="n">
         <v>8.91</v>
@@ -15139,7 +15141,7 @@
         <v>16.55</v>
       </c>
       <c r="BM58" t="n">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="BN58" t="n">
         <v>0</v>
@@ -15158,10 +15160,10 @@
         </is>
       </c>
       <c r="BR58" t="n">
-        <v>0.359</v>
+        <v>0.4972</v>
       </c>
       <c r="BS58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT58" t="n">
         <v>0</v>
@@ -15170,29 +15172,29 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>LUTS</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>UNINDEX</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>LUTS</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>UNINDEX</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E59" t="n">
         <v>1.01</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0182</v>
+        <v>0.0197</v>
       </c>
       <c r="G59" t="n">
         <v>0.0071</v>
@@ -15214,22 +15216,22 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="n">
-        <v>43540723</v>
+        <v>44887554</v>
       </c>
       <c r="O59" t="n">
         <v>360020900</v>
       </c>
       <c r="P59" t="n">
-        <v>8.269</v>
+        <v>8.021000000000001</v>
       </c>
       <c r="Q59" t="n">
-        <v>80050754</v>
+        <v>85102067</v>
       </c>
       <c r="R59" t="n">
-        <v>76721009</v>
+        <v>212155145</v>
       </c>
       <c r="S59" t="n">
-        <v>0.958</v>
+        <v>2.493</v>
       </c>
       <c r="T59" t="n">
         <v>0.7873</v>
@@ -15310,17 +15312,17 @@
         </is>
       </c>
       <c r="AP59" t="n">
-        <v>10994126112330</v>
+        <v>10994190401721</v>
       </c>
       <c r="AQ59" t="n">
-        <v>425816041</v>
+        <v>433432606</v>
       </c>
       <c r="AR59" t="n">
-        <v>69.12</v>
+        <v>70</v>
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:24</t>
+          <t>2026-09-11 18:20:19</t>
         </is>
       </c>
       <c r="AT59" t="n">
@@ -15373,7 +15375,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 139.2% above EMA200, MACD below signal (bearish), RSI in healthy bullish zone (61.8), volume 8.27x average, accumulation (ADL rising over last 20d); score=64.2/100; entry: enhanced entry at VWMA (overbought (RSI: 61.8)), +0.35% buffer</t>
+          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 139.2% above EMA200, MACD below signal (bearish), RSI in healthy bullish zone (61.8), volume 8.02x average, buy-volume spike (2.49x), accumulation (ADL rising over last 20d); score=64.2/100; entry: enhanced entry at VWMA (overbought (RSI: 61.8)), +0.35% buffer</t>
         </is>
       </c>
       <c r="BI59" t="n">
@@ -15420,29 +15422,29 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>INFI</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>UNINDEX</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>INFI</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>UNINDEX</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E60" t="n">
         <v>146.5</v>
       </c>
       <c r="F60" t="n">
-        <v>2.8788</v>
+        <v>2.8606</v>
       </c>
       <c r="G60" t="n">
         <v>0.1888</v>
@@ -15464,22 +15466,22 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="n">
-        <v>141558</v>
+        <v>141333</v>
       </c>
       <c r="O60" t="n">
         <v>85413</v>
       </c>
       <c r="P60" t="n">
-        <v>0.603</v>
+        <v>0.604</v>
       </c>
       <c r="Q60" t="n">
-        <v>106579</v>
+        <v>99373</v>
       </c>
       <c r="R60" t="n">
-        <v>47049</v>
+        <v>14236</v>
       </c>
       <c r="S60" t="n">
-        <v>0.441</v>
+        <v>0.143</v>
       </c>
       <c r="T60" t="n">
         <v>140.66</v>
@@ -15560,17 +15562,17 @@
         </is>
       </c>
       <c r="AP60" t="n">
-        <v>1585414365865</v>
+        <v>1585414308923</v>
       </c>
       <c r="AQ60" t="n">
-        <v>-2643665</v>
+        <v>-2234850</v>
       </c>
       <c r="AR60" t="n">
-        <v>68.48999999999999</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:24</t>
+          <t>2026-09-11 18:20:19</t>
         </is>
       </c>
       <c r="AT60" t="n">
@@ -15649,19 +15651,19 @@
       </c>
       <c r="BP60" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="BQ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="BR60" t="n">
-        <v>0</v>
+        <v>0.3585</v>
       </c>
       <c r="BS60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT60" t="n">
         <v>0</v>
@@ -15670,29 +15672,29 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>EPCO</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>UNINDEX</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>EPCO</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>UNINDEX</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E61" t="n">
         <v>11.72</v>
       </c>
       <c r="F61" t="n">
-        <v>0.2175</v>
+        <v>0.2288</v>
       </c>
       <c r="G61" t="n">
         <v>0.0625</v>
@@ -15702,42 +15704,40 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J61" t="n">
-        <v>11.2275</v>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>USD-Comparison (fallback)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="n">
-        <v>1689609</v>
+        <v>1720819</v>
       </c>
       <c r="O61" t="n">
         <v>8286753</v>
       </c>
       <c r="P61" t="n">
-        <v>4.905</v>
+        <v>4.816</v>
       </c>
       <c r="Q61" t="n">
-        <v>689490</v>
+        <v>783359</v>
       </c>
       <c r="R61" t="n">
-        <v>290439</v>
+        <v>4724906</v>
       </c>
       <c r="S61" t="n">
-        <v>0.421</v>
+        <v>6.032</v>
       </c>
       <c r="T61" t="n">
         <v>10.8</v>
       </c>
       <c r="U61" t="n">
-        <v>11.74</v>
+        <v>13.05</v>
       </c>
       <c r="V61" t="n">
         <v>10.8656</v>
@@ -15812,17 +15812,17 @@
         </is>
       </c>
       <c r="AP61" t="n">
-        <v>46479063978582</v>
+        <v>46479065141640</v>
       </c>
       <c r="AQ61" t="n">
-        <v>-8971179</v>
+        <v>-6893715</v>
       </c>
       <c r="AR61" t="n">
-        <v>67.86</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="AS61" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:24</t>
+          <t>2026-09-11 18:20:19</t>
         </is>
       </c>
       <c r="AT61" t="n">
@@ -15875,7 +15875,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 28.7% above EMA200, MACD below signal (bearish), RSI in healthy bullish zone (59.1), volume 4.91x average, distribution (ADL falling over last 20d); score=55.6/100; entry: enhanced entry at VWMA (overbought (RSI: 59.1)), +0.35% buffer</t>
+          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 28.7% above EMA200, MACD below signal (bearish), RSI in healthy bullish zone (59.1), volume 4.82x average, buy-volume spike (6.03x), distribution (ADL falling over last 20d); score=55.6/100; entry: enhanced entry at VWMA (overbought (RSI: 59.1)), +0.35% buffer</t>
         </is>
       </c>
       <c r="BI61" t="n">
@@ -15910,7 +15910,7 @@
         </is>
       </c>
       <c r="BR61" t="n">
-        <v>0.4274</v>
+        <v>0.459</v>
       </c>
       <c r="BS61" t="n">
         <v>0</v>
@@ -15922,29 +15922,29 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>EGAS</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>EGX33</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>EGAS</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>EGX33</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E62" t="n">
         <v>58.47</v>
       </c>
       <c r="F62" t="n">
-        <v>1.15</v>
+        <v>1.1417</v>
       </c>
       <c r="G62" t="n">
         <v>0.4709</v>
@@ -15958,7 +15958,7 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>62.0255</v>
+        <v>61.8914</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -15969,25 +15969,25 @@
         <v>11.54</v>
       </c>
       <c r="M62" t="n">
-        <v>5.0821</v>
+        <v>5.0674</v>
       </c>
       <c r="N62" t="n">
-        <v>217928</v>
+        <v>214622</v>
       </c>
       <c r="O62" t="n">
         <v>65658</v>
       </c>
       <c r="P62" t="n">
-        <v>0.301</v>
+        <v>0.306</v>
       </c>
       <c r="Q62" t="n">
-        <v>119206</v>
+        <v>117650</v>
       </c>
       <c r="R62" t="n">
-        <v>106776</v>
+        <v>12754</v>
       </c>
       <c r="S62" t="n">
-        <v>0.896</v>
+        <v>0.108</v>
       </c>
       <c r="T62" t="n">
         <v>55.21</v>
@@ -16068,17 +16068,17 @@
         </is>
       </c>
       <c r="AP62" t="n">
-        <v>-16271596571527</v>
+        <v>-16271595496252</v>
       </c>
       <c r="AQ62" t="n">
-        <v>-1716312</v>
+        <v>-1579322</v>
       </c>
       <c r="AR62" t="n">
-        <v>63.42</v>
+        <v>63.44</v>
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:24</t>
+          <t>2026-09-11 18:20:19</t>
         </is>
       </c>
       <c r="AT62" t="n">
@@ -16178,29 +16178,29 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>MASR</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>EGX33</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>MASR</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>EGX33</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E63" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="F63" t="n">
-        <v>0.1612</v>
+        <v>0.1621</v>
       </c>
       <c r="G63" t="n">
         <v>0.0591</v>
@@ -16214,7 +16214,7 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>26.2514</v>
+        <v>26.4598</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -16225,25 +16225,25 @@
         <v>2.97</v>
       </c>
       <c r="M63" t="n">
-        <v>2.7658</v>
+        <v>2.7927</v>
       </c>
       <c r="N63" t="n">
-        <v>7364284</v>
+        <v>7373339</v>
       </c>
       <c r="O63" t="n">
         <v>6640824</v>
       </c>
       <c r="P63" t="n">
-        <v>0.902</v>
+        <v>0.901</v>
       </c>
       <c r="Q63" t="n">
-        <v>5066730</v>
+        <v>4859491</v>
       </c>
       <c r="R63" t="n">
-        <v>2733789</v>
+        <v>3873827</v>
       </c>
       <c r="S63" t="n">
-        <v>0.54</v>
+        <v>0.797</v>
       </c>
       <c r="T63" t="n">
         <v>7.79</v>
@@ -16322,17 +16322,17 @@
         </is>
       </c>
       <c r="AP63" t="n">
-        <v>-972415626</v>
+        <v>-971308795</v>
       </c>
       <c r="AQ63" t="n">
-        <v>20732811</v>
+        <v>18406674</v>
       </c>
       <c r="AR63" t="n">
-        <v>61.65</v>
+        <v>61.83</v>
       </c>
       <c r="AS63" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:24</t>
+          <t>2026-09-11 18:20:19</t>
         </is>
       </c>
       <c r="AT63" t="n">
@@ -16411,19 +16411,19 @@
       </c>
       <c r="BP63" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="BQ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="BR63" t="n">
-        <v>0</v>
+        <v>0.3386</v>
       </c>
       <c r="BS63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT63" t="n">
         <v>0</v>
@@ -16432,29 +16432,29 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>OLFI</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>EGX33</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>OLFI</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>EGX33</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E64" t="n">
         <v>22.58</v>
       </c>
       <c r="F64" t="n">
-        <v>0.4473</v>
+        <v>0.4409</v>
       </c>
       <c r="G64" t="n">
         <v>0.1139</v>
@@ -16468,7 +16468,7 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>34.0806</v>
+        <v>33.7846</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -16479,25 +16479,25 @@
         <v>5.56</v>
       </c>
       <c r="M64" t="n">
-        <v>4.1014</v>
+        <v>4.0601</v>
       </c>
       <c r="N64" t="n">
-        <v>803055</v>
+        <v>804267</v>
       </c>
       <c r="O64" t="n">
         <v>576388</v>
       </c>
       <c r="P64" t="n">
-        <v>0.718</v>
+        <v>0.717</v>
       </c>
       <c r="Q64" t="n">
-        <v>812956</v>
+        <v>752022</v>
       </c>
       <c r="R64" t="n">
-        <v>175621</v>
+        <v>220948</v>
       </c>
       <c r="S64" t="n">
-        <v>0.216</v>
+        <v>0.294</v>
       </c>
       <c r="T64" t="n">
         <v>22.25</v>
@@ -16578,17 +16578,17 @@
         </is>
       </c>
       <c r="AP64" t="n">
-        <v>66998393997716</v>
+        <v>66998392895613</v>
       </c>
       <c r="AQ64" t="n">
-        <v>2825845</v>
+        <v>-155545</v>
       </c>
       <c r="AR64" t="n">
-        <v>57.75</v>
+        <v>57.73</v>
       </c>
       <c r="AS64" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:24</t>
+          <t>2026-09-11 18:20:19</t>
         </is>
       </c>
       <c r="AT64" t="n">
@@ -16636,16 +16636,16 @@
       </c>
       <c r="BG64" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Avoid</t>
         </is>
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>EMA50 &gt; EMA200, price above EMA200, Diamond Cross (EMA20&gt;EMA50), price 0.6% above EMA200, MACD below signal (bearish), RSI neutral-firm (42.6), accumulation (ADL rising over last 20d), price near support; score=43.4/100; entry: enhanced entry at Swing Support (neutral (RSI: 42.6)), +0.35% buffer</t>
+          <t>EMA50 &gt; EMA200, price above EMA200, Diamond Cross (EMA20&gt;EMA50), price 0.6% above EMA200, MACD below signal (bearish), RSI neutral-firm (42.6), distribution (ADL falling over last 20d), price near support; score=33.0/100; entry: enhanced entry at Swing Support (neutral (RSI: 42.6)), +0.35% buffer</t>
         </is>
       </c>
       <c r="BI64" t="n">
-        <v>43.35</v>
+        <v>32.98</v>
       </c>
       <c r="BJ64" t="n">
         <v>5.61</v>
@@ -16660,57 +16660,57 @@
         <v>0</v>
       </c>
       <c r="BN64" t="n">
-        <v>10.38</v>
+        <v>0</v>
       </c>
       <c r="BO64" t="n">
         <v>10.82</v>
       </c>
       <c r="BP64" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="BQ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Avoid</t>
         </is>
       </c>
       <c r="BR64" t="n">
-        <v>0</v>
+        <v>0.3962</v>
       </c>
       <c r="BS64" t="n">
         <v>0</v>
       </c>
       <c r="BT64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ORHD</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>EGX30</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>ORHD</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>EGX30</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E65" t="n">
         <v>43.2</v>
       </c>
       <c r="F65" t="n">
-        <v>0.8188</v>
+        <v>0.8435</v>
       </c>
       <c r="G65" t="n">
         <v>0.0441</v>
@@ -16724,7 +16724,7 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>124.4776</v>
+        <v>128.1509</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -16735,25 +16735,25 @@
         <v>2.87</v>
       </c>
       <c r="M65" t="n">
-        <v>14.5618</v>
+        <v>15.0675</v>
       </c>
       <c r="N65" t="n">
-        <v>3915333</v>
+        <v>3921263</v>
       </c>
       <c r="O65" t="n">
         <v>5987926</v>
       </c>
       <c r="P65" t="n">
-        <v>1.529</v>
+        <v>1.527</v>
       </c>
       <c r="Q65" t="n">
-        <v>1395123</v>
+        <v>1493135</v>
       </c>
       <c r="R65" t="n">
-        <v>400716</v>
+        <v>5229973</v>
       </c>
       <c r="S65" t="n">
-        <v>0.287</v>
+        <v>3.503</v>
       </c>
       <c r="T65" t="n">
         <v>40.85</v>
@@ -16834,17 +16834,17 @@
         </is>
       </c>
       <c r="AP65" t="n">
-        <v>-23122922360456</v>
+        <v>-23122917888436</v>
       </c>
       <c r="AQ65" t="n">
-        <v>-1649010</v>
+        <v>3560800</v>
       </c>
       <c r="AR65" t="n">
-        <v>63.09</v>
+        <v>63.22</v>
       </c>
       <c r="AS65" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:24</t>
+          <t>2026-09-11 18:20:19</t>
         </is>
       </c>
       <c r="AT65" t="n">
@@ -16892,16 +16892,16 @@
       </c>
       <c r="BG65" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 30.3% above EMA200, MACD below signal (bearish), RSI in healthy bullish zone (59.6), distribution (ADL falling over last 20d); score=39.4/100; entry: enhanced entry at VWMA (overbought (RSI: 59.6)), +0.35% buffer</t>
+          <t>price &gt; EMA50 &gt; EMA200 (strong bullish alignment), Diamond Cross (EMA20&gt;EMA50), price 30.3% above EMA200, MACD below signal (bearish), RSI in healthy bullish zone (59.6), buy-volume spike (3.50x), accumulation (ADL rising over last 20d); score=64.2/100; entry: enhanced entry at VWMA (overbought (RSI: 59.6)), +0.35% buffer</t>
         </is>
       </c>
       <c r="BI65" t="n">
-        <v>39.41</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="BJ65" t="n">
         <v>10.09</v>
@@ -16913,10 +16913,10 @@
         <v>27.58</v>
       </c>
       <c r="BM65" t="n">
-        <v>1.74</v>
+        <v>17.9</v>
       </c>
       <c r="BN65" t="n">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="BO65" t="n">
         <v>0</v>
@@ -16944,22 +16944,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>COPR</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>UNINDEX</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>COPR</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>UNINDEX</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -16980,7 +16980,7 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>0.4967</v>
+        <v>0.5068</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -16990,20 +16990,22 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="n">
-        <v>58101833</v>
+        <v>58125363</v>
       </c>
       <c r="O66" t="n">
         <v>32571441</v>
       </c>
       <c r="P66" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q66" t="n">
-        <v>59536425</v>
-      </c>
-      <c r="R66" t="inlineStr"/>
+        <v>59406139</v>
+      </c>
+      <c r="R66" t="n">
+        <v>15032990</v>
+      </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>0.253</v>
       </c>
       <c r="T66" t="inlineStr"/>
       <c r="U66" t="n">
@@ -17082,17 +17084,17 @@
         </is>
       </c>
       <c r="AP66" t="n">
-        <v>-8211728483236239</v>
+        <v>-8211728485741700</v>
       </c>
       <c r="AQ66" t="n">
-        <v>-273660918</v>
+        <v>-339151834</v>
       </c>
       <c r="AR66" t="n">
-        <v>61.09</v>
+        <v>61.01</v>
       </c>
       <c r="AS66" t="inlineStr">
         <is>
-          <t>2026-09-10 18:16:24</t>
+          <t>2026-09-11 18:20:19</t>
         </is>
       </c>
       <c r="AT66" t="n">
@@ -17171,19 +17173,19 @@
       </c>
       <c r="BP66" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="BQ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="BR66" t="n">
-        <v>0</v>
+        <v>0.3079</v>
       </c>
       <c r="BS66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT66" t="n">
         <v>0</v>
@@ -17333,7 +17335,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-09-10 18:17:05</t>
+          <t>2026-09-11 18:21:04</t>
         </is>
       </c>
     </row>
@@ -17390,7 +17392,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-09-10 18:17:05</t>
+          <t>2026-09-11 18:21:04</t>
         </is>
       </c>
     </row>

--- a/Stock_Analysis_Output.xlsx
+++ b/Stock_Analysis_Output.xlsx
@@ -794,7 +794,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -944,11 +944,11 @@
         <v>38586692</v>
       </c>
       <c r="AR2" t="n">
-        <v>58.09</v>
+        <v>58.07</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:09</t>
+          <t>2026-09-12 17:44:51</t>
         </is>
       </c>
       <c r="AT2" t="n">
@@ -1048,7 +1048,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AP3" t="n">
-        <v>22845653274216</v>
+        <v>22845653641477</v>
       </c>
       <c r="AQ3" t="n">
         <v>-2808339</v>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:09</t>
+          <t>2026-09-12 17:44:51</t>
         </is>
       </c>
       <c r="AT3" t="n">
@@ -1304,7 +1304,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1450,17 +1450,17 @@
         </is>
       </c>
       <c r="AP4" t="n">
-        <v>191059131617015</v>
+        <v>191059129458480</v>
       </c>
       <c r="AQ4" t="n">
         <v>-3623220</v>
       </c>
       <c r="AR4" t="n">
-        <v>63.1</v>
+        <v>63.27</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:09</t>
+          <t>2026-09-12 17:44:51</t>
         </is>
       </c>
       <c r="AT4" t="n">
@@ -1560,7 +1560,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:09</t>
+          <t>2026-09-12 17:44:51</t>
         </is>
       </c>
       <c r="AT5" t="n">
@@ -1816,7 +1816,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1962,17 +1962,17 @@
         </is>
       </c>
       <c r="AP6" t="n">
-        <v>5694284010333</v>
+        <v>5694284097516</v>
       </c>
       <c r="AQ6" t="n">
         <v>-489699</v>
       </c>
       <c r="AR6" t="n">
-        <v>63.72</v>
+        <v>63.71</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:09</t>
+          <t>2026-09-12 17:44:51</t>
         </is>
       </c>
       <c r="AT6" t="n">
@@ -2072,7 +2072,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2218,17 +2218,17 @@
         </is>
       </c>
       <c r="AP7" t="n">
-        <v>1905064156263</v>
+        <v>1905064026320</v>
       </c>
       <c r="AQ7" t="n">
         <v>-46309623</v>
       </c>
       <c r="AR7" t="n">
-        <v>62.43</v>
+        <v>62.27</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:09</t>
+          <t>2026-09-12 17:44:51</t>
         </is>
       </c>
       <c r="AT7" t="n">
@@ -2328,7 +2328,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2474,17 +2474,17 @@
         </is>
       </c>
       <c r="AP8" t="n">
-        <v>23880740703852</v>
+        <v>23880740635329</v>
       </c>
       <c r="AQ8" t="n">
         <v>-1774614</v>
       </c>
       <c r="AR8" t="n">
-        <v>59</v>
+        <v>58.98</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:09</t>
+          <t>2026-09-12 17:44:51</t>
         </is>
       </c>
       <c r="AT8" t="n">
@@ -2584,7 +2584,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2730,17 +2730,17 @@
         </is>
       </c>
       <c r="AP9" t="n">
-        <v>17855038528542</v>
+        <v>17855038334671</v>
       </c>
       <c r="AQ9" t="n">
         <v>-1155496</v>
       </c>
       <c r="AR9" t="n">
-        <v>68.61</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:09</t>
+          <t>2026-09-12 17:44:51</t>
         </is>
       </c>
       <c r="AT9" t="n">
@@ -2840,7 +2840,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:09</t>
+          <t>2026-09-12 17:44:51</t>
         </is>
       </c>
       <c r="AT10" t="n">
@@ -3078,7 +3078,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3228,11 +3228,11 @@
         <v>4558488</v>
       </c>
       <c r="AR11" t="n">
-        <v>59.53</v>
+        <v>59.56</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:09</t>
+          <t>2026-09-12 17:44:51</t>
         </is>
       </c>
       <c r="AT11" t="n">
@@ -3332,7 +3332,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:09</t>
+          <t>2026-09-12 17:44:51</t>
         </is>
       </c>
       <c r="AT12" t="n">
@@ -3588,7 +3588,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:09</t>
+          <t>2026-09-12 17:44:51</t>
         </is>
       </c>
       <c r="AT13" t="n">
@@ -3842,7 +3842,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3994,11 +3994,11 @@
         <v>-18845384</v>
       </c>
       <c r="AR14" t="n">
-        <v>66.65000000000001</v>
+        <v>66.64</v>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:09</t>
+          <t>2026-09-12 17:44:51</t>
         </is>
       </c>
       <c r="AT14" t="n">
@@ -4098,7 +4098,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:09</t>
+          <t>2026-09-12 17:44:51</t>
         </is>
       </c>
       <c r="AT15" t="n">
@@ -4346,7 +4346,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:09</t>
+          <t>2026-09-12 17:44:51</t>
         </is>
       </c>
       <c r="AT16" t="n">
@@ -4598,7 +4598,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:09</t>
+          <t>2026-09-12 17:44:51</t>
         </is>
       </c>
       <c r="AT17" t="n">
@@ -4852,7 +4852,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>169.9351</v>
+        <v>168.5906</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -4998,17 +4998,17 @@
         </is>
       </c>
       <c r="AP18" t="n">
-        <v>282706777584</v>
+        <v>282706802803</v>
       </c>
       <c r="AQ18" t="n">
         <v>-728003</v>
       </c>
       <c r="AR18" t="n">
-        <v>61.51</v>
+        <v>61.52</v>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:09</t>
+          <t>2026-09-12 17:44:51</t>
         </is>
       </c>
       <c r="AT18" t="n">
@@ -5108,7 +5108,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:09</t>
+          <t>2026-09-12 17:44:51</t>
         </is>
       </c>
       <c r="AT19" t="n">
@@ -5358,7 +5358,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5401,8 +5401,12 @@
           <t>USD-Comparison (fallback)</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.9878</v>
+      </c>
       <c r="N20" t="n">
         <v>4391535</v>
       </c>
@@ -5500,17 +5504,17 @@
         </is>
       </c>
       <c r="AP20" t="n">
-        <v>1899887912587</v>
+        <v>1899887437378</v>
       </c>
       <c r="AQ20" t="n">
         <v>7517778</v>
       </c>
       <c r="AR20" t="n">
-        <v>66.98999999999999</v>
+        <v>66.98</v>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:09</t>
+          <t>2026-09-12 17:44:51</t>
         </is>
       </c>
       <c r="AT20" t="n">
@@ -5610,7 +5614,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5766,7 +5770,7 @@
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:09</t>
+          <t>2026-09-12 17:44:51</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -5844,7 +5848,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5990,7 +5994,7 @@
         </is>
       </c>
       <c r="AP22" t="n">
-        <v>931170803836016</v>
+        <v>931170721062990</v>
       </c>
       <c r="AQ22" t="n">
         <v>-2906031</v>
@@ -6000,7 +6004,7 @@
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:09</t>
+          <t>2026-09-12 17:44:51</t>
         </is>
       </c>
       <c r="AT22" t="n">
@@ -6100,7 +6104,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6252,11 +6256,11 @@
         <v>-2945970</v>
       </c>
       <c r="AR23" t="n">
-        <v>59.6</v>
+        <v>59.56</v>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:09</t>
+          <t>2026-09-12 17:44:51</t>
         </is>
       </c>
       <c r="AT23" t="n">
@@ -6356,7 +6360,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6502,17 +6506,17 @@
         </is>
       </c>
       <c r="AP24" t="n">
-        <v>-25967528864752</v>
+        <v>-25967528266975</v>
       </c>
       <c r="AQ24" t="n">
         <v>-1175555</v>
       </c>
       <c r="AR24" t="n">
-        <v>67.94</v>
+        <v>67.88</v>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:09</t>
+          <t>2026-09-12 17:44:51</t>
         </is>
       </c>
       <c r="AT24" t="n">
@@ -6612,7 +6616,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6752,17 +6756,17 @@
         </is>
       </c>
       <c r="AP25" t="n">
-        <v>3322247140936</v>
+        <v>3322247912100</v>
       </c>
       <c r="AQ25" t="n">
         <v>-4193070</v>
       </c>
       <c r="AR25" t="n">
-        <v>68.27</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:09</t>
+          <t>2026-09-12 17:44:51</t>
         </is>
       </c>
       <c r="AT25" t="n">
@@ -6862,7 +6866,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -7006,7 +7010,7 @@
         </is>
       </c>
       <c r="AP26" t="n">
-        <v>99374626378795</v>
+        <v>99374623625833</v>
       </c>
       <c r="AQ26" t="n">
         <v>-3334866</v>
@@ -7016,7 +7020,7 @@
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:09</t>
+          <t>2026-09-12 17:44:51</t>
         </is>
       </c>
       <c r="AT26" t="n">
@@ -7116,7 +7120,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7268,7 +7272,7 @@
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:09</t>
+          <t>2026-09-12 17:44:51</t>
         </is>
       </c>
       <c r="AT27" t="n">
@@ -7368,7 +7372,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7518,7 +7522,7 @@
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:09</t>
+          <t>2026-09-12 17:44:51</t>
         </is>
       </c>
       <c r="AT28" t="n">
@@ -7618,7 +7622,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7766,7 +7770,7 @@
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:09</t>
+          <t>2026-09-12 17:44:51</t>
         </is>
       </c>
       <c r="AT29" t="n">
@@ -7866,7 +7870,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -8022,7 +8026,7 @@
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:09</t>
+          <t>2026-09-12 17:44:51</t>
         </is>
       </c>
       <c r="AT30" t="n">
@@ -8122,7 +8126,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8270,7 +8274,7 @@
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:09</t>
+          <t>2026-09-12 17:44:51</t>
         </is>
       </c>
       <c r="AT31" t="n">
@@ -8370,7 +8374,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8518,7 +8522,7 @@
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:09</t>
+          <t>2026-09-12 17:44:51</t>
         </is>
       </c>
       <c r="AT32" t="n">
@@ -8618,7 +8622,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8774,7 +8778,7 @@
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:09</t>
+          <t>2026-09-12 17:44:51</t>
         </is>
       </c>
       <c r="AT33" t="n">
@@ -8874,7 +8878,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -9026,7 +9030,7 @@
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:09</t>
+          <t>2026-09-12 17:44:51</t>
         </is>
       </c>
       <c r="AT34" t="n">
@@ -9126,7 +9130,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -9280,7 +9284,7 @@
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:09</t>
+          <t>2026-09-12 17:44:51</t>
         </is>
       </c>
       <c r="AT35" t="n">
@@ -9380,7 +9384,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -9536,7 +9540,7 @@
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:09</t>
+          <t>2026-09-12 17:44:51</t>
         </is>
       </c>
       <c r="AT36" t="n">
@@ -9636,7 +9640,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -9792,7 +9796,7 @@
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:09</t>
+          <t>2026-09-12 17:44:51</t>
         </is>
       </c>
       <c r="AT37" t="n">
@@ -9892,7 +9896,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -10048,7 +10052,7 @@
       </c>
       <c r="AS38" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:09</t>
+          <t>2026-09-12 17:44:51</t>
         </is>
       </c>
       <c r="AT38" t="n">
@@ -10148,7 +10152,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -10300,7 +10304,7 @@
       </c>
       <c r="AS39" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:09</t>
+          <t>2026-09-12 17:44:51</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -10378,7 +10382,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -10528,7 +10532,7 @@
       </c>
       <c r="AS40" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:19</t>
+          <t>2026-09-12 17:44:59</t>
         </is>
       </c>
       <c r="AT40" t="n">
@@ -10628,7 +10632,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -10782,7 +10786,7 @@
       </c>
       <c r="AS41" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:19</t>
+          <t>2026-09-12 17:44:59</t>
         </is>
       </c>
       <c r="AT41" t="n">
@@ -10882,7 +10886,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -11026,7 +11030,7 @@
         </is>
       </c>
       <c r="AP42" t="n">
-        <v>11377379707483</v>
+        <v>11377379746674</v>
       </c>
       <c r="AQ42" t="n">
         <v>16871502</v>
@@ -11036,7 +11040,7 @@
       </c>
       <c r="AS42" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:19</t>
+          <t>2026-09-12 17:44:59</t>
         </is>
       </c>
       <c r="AT42" t="n">
@@ -11136,7 +11140,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -11286,7 +11290,7 @@
       </c>
       <c r="AS43" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:19</t>
+          <t>2026-09-12 17:44:59</t>
         </is>
       </c>
       <c r="AT43" t="n">
@@ -11386,7 +11390,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -11540,7 +11544,7 @@
       </c>
       <c r="AS44" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:19</t>
+          <t>2026-09-12 17:44:59</t>
         </is>
       </c>
       <c r="AT44" t="n">
@@ -11640,7 +11644,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -11792,7 +11796,7 @@
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:19</t>
+          <t>2026-09-12 17:44:59</t>
         </is>
       </c>
       <c r="AT45" t="n">
@@ -11892,7 +11896,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -12042,7 +12046,7 @@
       </c>
       <c r="AS46" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:19</t>
+          <t>2026-09-12 17:44:59</t>
         </is>
       </c>
       <c r="AT46" t="n">
@@ -12142,7 +12146,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -12298,7 +12302,7 @@
       </c>
       <c r="AS47" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:19</t>
+          <t>2026-09-12 17:44:59</t>
         </is>
       </c>
       <c r="AT47" t="n">
@@ -12398,7 +12402,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -12554,7 +12558,7 @@
       </c>
       <c r="AS48" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:19</t>
+          <t>2026-09-12 17:44:59</t>
         </is>
       </c>
       <c r="AT48" t="n">
@@ -12654,7 +12658,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -12802,7 +12806,7 @@
       </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:19</t>
+          <t>2026-09-12 17:44:59</t>
         </is>
       </c>
       <c r="AT49" t="n">
@@ -12902,7 +12906,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -13044,7 +13048,7 @@
         </is>
       </c>
       <c r="AP50" t="n">
-        <v>37433667729869</v>
+        <v>37433669515506</v>
       </c>
       <c r="AQ50" t="n">
         <v>-79231</v>
@@ -13054,7 +13058,7 @@
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:19</t>
+          <t>2026-09-12 17:44:59</t>
         </is>
       </c>
       <c r="AT50" t="n">
@@ -13154,7 +13158,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -13294,17 +13298,17 @@
         </is>
       </c>
       <c r="AP51" t="n">
-        <v>704433059945748</v>
+        <v>704433058071314</v>
       </c>
       <c r="AQ51" t="n">
         <v>-24080</v>
       </c>
       <c r="AR51" t="n">
-        <v>66.45</v>
+        <v>66.44</v>
       </c>
       <c r="AS51" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:19</t>
+          <t>2026-09-12 17:44:59</t>
         </is>
       </c>
       <c r="AT51" t="n">
@@ -13404,7 +13408,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -13550,7 +13554,7 @@
         </is>
       </c>
       <c r="AP52" t="n">
-        <v>56932924313514</v>
+        <v>56932924066091</v>
       </c>
       <c r="AQ52" t="n">
         <v>354089</v>
@@ -13560,7 +13564,7 @@
       </c>
       <c r="AS52" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:19</t>
+          <t>2026-09-12 17:44:59</t>
         </is>
       </c>
       <c r="AT52" t="n">
@@ -13660,7 +13664,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -13798,17 +13802,17 @@
         </is>
       </c>
       <c r="AP53" t="n">
-        <v>107581379164492</v>
+        <v>107581383057511</v>
       </c>
       <c r="AQ53" t="n">
         <v>-569283</v>
       </c>
       <c r="AR53" t="n">
-        <v>68.64</v>
+        <v>68.63</v>
       </c>
       <c r="AS53" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:19</t>
+          <t>2026-09-12 17:44:59</t>
         </is>
       </c>
       <c r="AT53" t="n">
@@ -13908,7 +13912,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -14052,7 +14056,7 @@
         </is>
       </c>
       <c r="AP54" t="n">
-        <v>303724404780082</v>
+        <v>303724424537675</v>
       </c>
       <c r="AQ54" t="n">
         <v>142151866</v>
@@ -14062,7 +14066,7 @@
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:19</t>
+          <t>2026-09-12 17:44:59</t>
         </is>
       </c>
       <c r="AT54" t="n">
@@ -14162,7 +14166,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -14306,17 +14310,17 @@
         </is>
       </c>
       <c r="AP55" t="n">
-        <v>715005636163</v>
+        <v>715005648962</v>
       </c>
       <c r="AQ55" t="n">
         <v>3379016</v>
       </c>
       <c r="AR55" t="n">
-        <v>66.23</v>
+        <v>66.17</v>
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:19</t>
+          <t>2026-09-12 17:44:59</t>
         </is>
       </c>
       <c r="AT55" t="n">
@@ -14416,7 +14420,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -14562,7 +14566,7 @@
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:19</t>
+          <t>2026-09-12 17:44:59</t>
         </is>
       </c>
       <c r="AT56" t="n">
@@ -14662,7 +14666,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -14806,7 +14810,7 @@
         </is>
       </c>
       <c r="AP57" t="n">
-        <v>142484483774628</v>
+        <v>142484483729397</v>
       </c>
       <c r="AQ57" t="n">
         <v>-849288</v>
@@ -14816,7 +14820,7 @@
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:19</t>
+          <t>2026-09-12 17:44:59</t>
         </is>
       </c>
       <c r="AT57" t="n">
@@ -14916,7 +14920,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -15072,7 +15076,7 @@
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:19</t>
+          <t>2026-09-12 17:44:59</t>
         </is>
       </c>
       <c r="AT58" t="n">
@@ -15172,7 +15176,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -15322,7 +15326,7 @@
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:19</t>
+          <t>2026-09-12 17:44:59</t>
         </is>
       </c>
       <c r="AT59" t="n">
@@ -15422,7 +15426,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -15572,7 +15576,7 @@
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:19</t>
+          <t>2026-09-12 17:44:59</t>
         </is>
       </c>
       <c r="AT60" t="n">
@@ -15672,7 +15676,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -15822,7 +15826,7 @@
       </c>
       <c r="AS61" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:19</t>
+          <t>2026-09-12 17:44:59</t>
         </is>
       </c>
       <c r="AT61" t="n">
@@ -15922,7 +15926,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -16068,7 +16072,7 @@
         </is>
       </c>
       <c r="AP62" t="n">
-        <v>-16271595496252</v>
+        <v>-16271596250978</v>
       </c>
       <c r="AQ62" t="n">
         <v>-1579322</v>
@@ -16078,7 +16082,7 @@
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:19</t>
+          <t>2026-09-12 17:44:59</t>
         </is>
       </c>
       <c r="AT62" t="n">
@@ -16178,7 +16182,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -16328,11 +16332,11 @@
         <v>18406674</v>
       </c>
       <c r="AR63" t="n">
-        <v>61.83</v>
+        <v>61.69</v>
       </c>
       <c r="AS63" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:19</t>
+          <t>2026-09-12 17:44:59</t>
         </is>
       </c>
       <c r="AT63" t="n">
@@ -16432,7 +16436,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -16578,17 +16582,17 @@
         </is>
       </c>
       <c r="AP64" t="n">
-        <v>66998392895613</v>
+        <v>66998394913841</v>
       </c>
       <c r="AQ64" t="n">
         <v>-155545</v>
       </c>
       <c r="AR64" t="n">
-        <v>57.73</v>
+        <v>57.77</v>
       </c>
       <c r="AS64" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:19</t>
+          <t>2026-09-12 17:44:59</t>
         </is>
       </c>
       <c r="AT64" t="n">
@@ -16688,7 +16692,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -16844,7 +16848,7 @@
       </c>
       <c r="AS65" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:19</t>
+          <t>2026-09-12 17:44:59</t>
         </is>
       </c>
       <c r="AT65" t="n">
@@ -16944,7 +16948,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -17094,7 +17098,7 @@
       </c>
       <c r="AS66" t="inlineStr">
         <is>
-          <t>2026-09-11 18:20:19</t>
+          <t>2026-09-12 17:44:59</t>
         </is>
       </c>
       <c r="AT66" t="n">
@@ -17335,7 +17339,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-09-11 18:21:04</t>
+          <t>2026-09-12 17:45:38</t>
         </is>
       </c>
     </row>
@@ -17392,7 +17396,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-09-11 18:21:04</t>
+          <t>2026-09-12 17:45:38</t>
         </is>
       </c>
     </row>
